--- a/Stepping into the World of Excel ASING/Stepping into the World of Excel- assingment 1.xlsx
+++ b/Stepping into the World of Excel ASING/Stepping into the World of Excel- assingment 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/spandanshelar/Documents/01-excle/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/spandanshelar/Documents/01-excle/Stepping into the World of Excel ASING/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EDF631B-B1B1-A546-9589-F2608028039F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A8AF2C-B5BB-B647-9B9E-25F321A5ED98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,10 +273,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy\,\ ddd"/>
-    <numFmt numFmtId="169" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;₹&quot;* #,##0.00_);_(&quot;₹&quot;* \(#,##0.00\);_(&quot;₹&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\,\ ddd"/>
+    <numFmt numFmtId="167" formatCode="&quot;₹&quot;#,##0.00"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -290,32 +291,38 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -376,11 +383,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -388,17 +394,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="168" formatCode="dd/mm/yyyy\,\ ddd"/>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\,\ ddd"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -672,8 +679,8 @@
     <col min="4" max="4" width="12.1640625" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="13" customWidth="1"/>
     <col min="9" max="26" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -722,7 +729,7 @@
       <c r="F2" s="4">
         <v>33</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H2" s="19">
@@ -748,7 +755,7 @@
       <c r="F3" s="4">
         <v>87</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H3" s="19">
@@ -774,7 +781,7 @@
       <c r="F4" s="4">
         <v>58</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H4" s="19">
@@ -800,7 +807,7 @@
       <c r="F5" s="4">
         <v>82</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="18">
         <v>1.87</v>
       </c>
       <c r="H5" s="19">
@@ -826,7 +833,7 @@
       <c r="F6" s="4">
         <v>38</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H6" s="19">
@@ -852,7 +859,7 @@
       <c r="F7" s="4">
         <v>54</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="18">
         <v>1.77</v>
       </c>
       <c r="H7" s="19">
@@ -878,7 +885,7 @@
       <c r="F8" s="4">
         <v>149</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H8" s="19">
@@ -904,7 +911,7 @@
       <c r="F9" s="4">
         <v>51</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="18">
         <v>1.77</v>
       </c>
       <c r="H9" s="19">
@@ -930,7 +937,7 @@
       <c r="F10" s="4">
         <v>100</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="18">
         <v>1.77</v>
       </c>
       <c r="H10" s="19">
@@ -956,7 +963,7 @@
       <c r="F11" s="4">
         <v>28</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="18">
         <v>1.35</v>
       </c>
       <c r="H11" s="19">
@@ -982,7 +989,7 @@
       <c r="F12" s="4">
         <v>36</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H12" s="19">
@@ -1008,7 +1015,7 @@
       <c r="F13" s="4">
         <v>31</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H13" s="19">
@@ -1034,7 +1041,7 @@
       <c r="F14" s="4">
         <v>28</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H14" s="19">
@@ -1060,7 +1067,7 @@
       <c r="F15" s="4">
         <v>44</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H15" s="19">
@@ -1086,7 +1093,7 @@
       <c r="F16" s="4">
         <v>23</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="18">
         <v>1.77</v>
       </c>
       <c r="H16" s="19">
@@ -1112,7 +1119,7 @@
       <c r="F17" s="4">
         <v>27</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="18">
         <v>1.35</v>
       </c>
       <c r="H17" s="19">
@@ -1138,7 +1145,7 @@
       <c r="F18" s="4">
         <v>43</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H18" s="19">
@@ -1164,7 +1171,7 @@
       <c r="F19" s="4">
         <v>123</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="18">
         <v>2.84</v>
       </c>
       <c r="H19" s="19">
@@ -1190,7 +1197,7 @@
       <c r="F20" s="4">
         <v>42</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="18">
         <v>1.87</v>
       </c>
       <c r="H20" s="19">
@@ -1216,7 +1223,7 @@
       <c r="F21" s="4">
         <v>33</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="18">
         <v>2.84</v>
       </c>
       <c r="H21" s="19">
@@ -1242,7 +1249,7 @@
       <c r="F22" s="4">
         <v>85</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H22" s="19">
@@ -1268,7 +1275,7 @@
       <c r="F23" s="4">
         <v>30</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H23" s="19">
@@ -1294,7 +1301,7 @@
       <c r="F24" s="4">
         <v>61</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="18">
         <v>1.77</v>
       </c>
       <c r="H24" s="19">
@@ -1320,7 +1327,7 @@
       <c r="F25" s="4">
         <v>40</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H25" s="19">
@@ -1346,7 +1353,7 @@
       <c r="F26" s="4">
         <v>86</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H26" s="19">
@@ -1372,7 +1379,7 @@
       <c r="F27" s="4">
         <v>38</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="18">
         <v>1.7700000000000002</v>
       </c>
       <c r="H27" s="19">
@@ -1398,7 +1405,7 @@
       <c r="F28" s="4">
         <v>68</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="18">
         <v>1.68</v>
       </c>
       <c r="H28" s="19">
@@ -1424,7 +1431,7 @@
       <c r="F29" s="4">
         <v>39</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="18">
         <v>1.87</v>
       </c>
       <c r="H29" s="19">
@@ -1450,7 +1457,7 @@
       <c r="F30" s="4">
         <v>103</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="18">
         <v>1.87</v>
       </c>
       <c r="H30" s="19">
@@ -1476,7 +1483,7 @@
       <c r="F31" s="4">
         <v>193</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="18">
         <v>2.84</v>
       </c>
       <c r="H31" s="19">
@@ -1502,7 +1509,7 @@
       <c r="F32" s="4">
         <v>58</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="18">
         <v>1.77</v>
       </c>
       <c r="H32" s="19">
@@ -1528,7 +1535,7 @@
       <c r="F33" s="4">
         <v>68</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="18">
         <v>1.68</v>
       </c>
       <c r="H33" s="19">
@@ -1554,7 +1561,7 @@
       <c r="F34" s="4">
         <v>91</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="18">
         <v>1.77</v>
       </c>
       <c r="H34" s="19">
@@ -1580,7 +1587,7 @@
       <c r="F35" s="4">
         <v>23</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H35" s="19">
@@ -1606,7 +1613,7 @@
       <c r="F36" s="4">
         <v>28</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="18">
         <v>1.68</v>
       </c>
       <c r="H36" s="19">
@@ -1632,7 +1639,7 @@
       <c r="F37" s="4">
         <v>48</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H37" s="19">
@@ -1658,7 +1665,7 @@
       <c r="F38" s="4">
         <v>134</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="18">
         <v>1.68</v>
       </c>
       <c r="H38" s="19">
@@ -1684,7 +1691,7 @@
       <c r="F39" s="4">
         <v>20</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="18">
         <v>1.77</v>
       </c>
       <c r="H39" s="19">
@@ -1710,7 +1717,7 @@
       <c r="F40" s="4">
         <v>53</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="18">
         <v>1.77</v>
       </c>
       <c r="H40" s="19">
@@ -1736,7 +1743,7 @@
       <c r="F41" s="4">
         <v>64</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="18">
         <v>1.68</v>
       </c>
       <c r="H41" s="19">
@@ -1762,7 +1769,7 @@
       <c r="F42" s="4">
         <v>63</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="18">
         <v>1.87</v>
       </c>
       <c r="H42" s="19">
@@ -1788,7 +1795,7 @@
       <c r="F43" s="4">
         <v>105</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H43" s="19">
@@ -1814,7 +1821,7 @@
       <c r="F44" s="4">
         <v>138</v>
       </c>
-      <c r="G44" s="13">
+      <c r="G44" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H44" s="19">
@@ -1840,7 +1847,7 @@
       <c r="F45" s="4">
         <v>25</v>
       </c>
-      <c r="G45" s="13">
+      <c r="G45" s="18">
         <v>1.77</v>
       </c>
       <c r="H45" s="19">
@@ -1866,7 +1873,7 @@
       <c r="F46" s="4">
         <v>21</v>
       </c>
-      <c r="G46" s="13">
+      <c r="G46" s="18">
         <v>3.49</v>
       </c>
       <c r="H46" s="19">
@@ -1892,7 +1899,7 @@
       <c r="F47" s="4">
         <v>61</v>
       </c>
-      <c r="G47" s="13">
+      <c r="G47" s="18">
         <v>1.77</v>
       </c>
       <c r="H47" s="19">
@@ -1918,7 +1925,7 @@
       <c r="F48" s="4">
         <v>49</v>
       </c>
-      <c r="G48" s="13">
+      <c r="G48" s="18">
         <v>1.68</v>
       </c>
       <c r="H48" s="19">
@@ -1944,7 +1951,7 @@
       <c r="F49" s="4">
         <v>55</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H49" s="19">
@@ -1970,7 +1977,7 @@
       <c r="F50" s="4">
         <v>27</v>
       </c>
-      <c r="G50" s="13">
+      <c r="G50" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H50" s="19">
@@ -1996,7 +2003,7 @@
       <c r="F51" s="4">
         <v>58</v>
       </c>
-      <c r="G51" s="13">
+      <c r="G51" s="18">
         <v>1.77</v>
       </c>
       <c r="H51" s="19">
@@ -2022,7 +2029,7 @@
       <c r="F52" s="4">
         <v>33</v>
       </c>
-      <c r="G52" s="13">
+      <c r="G52" s="18">
         <v>3.49</v>
       </c>
       <c r="H52" s="19">
@@ -2048,7 +2055,7 @@
       <c r="F53" s="4">
         <v>288</v>
       </c>
-      <c r="G53" s="13">
+      <c r="G53" s="18">
         <v>2.84</v>
       </c>
       <c r="H53" s="19">
@@ -2074,7 +2081,7 @@
       <c r="F54" s="4">
         <v>76</v>
       </c>
-      <c r="G54" s="13">
+      <c r="G54" s="18">
         <v>1.87</v>
       </c>
       <c r="H54" s="19">
@@ -2100,7 +2107,7 @@
       <c r="F55" s="4">
         <v>42</v>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="18">
         <v>1.77</v>
       </c>
       <c r="H55" s="19">
@@ -2126,7 +2133,7 @@
       <c r="F56" s="4">
         <v>20</v>
       </c>
-      <c r="G56" s="13">
+      <c r="G56" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H56" s="19">
@@ -2152,7 +2159,7 @@
       <c r="F57" s="4">
         <v>75</v>
       </c>
-      <c r="G57" s="13">
+      <c r="G57" s="18">
         <v>1.77</v>
       </c>
       <c r="H57" s="19">
@@ -2178,7 +2185,7 @@
       <c r="F58" s="4">
         <v>38</v>
       </c>
-      <c r="G58" s="13">
+      <c r="G58" s="18">
         <v>3.49</v>
       </c>
       <c r="H58" s="19">
@@ -2204,7 +2211,7 @@
       <c r="F59" s="4">
         <v>306</v>
       </c>
-      <c r="G59" s="13">
+      <c r="G59" s="18">
         <v>1.77</v>
       </c>
       <c r="H59" s="19">
@@ -2230,7 +2237,7 @@
       <c r="F60" s="4">
         <v>28</v>
       </c>
-      <c r="G60" s="13">
+      <c r="G60" s="18">
         <v>1.68</v>
       </c>
       <c r="H60" s="19">
@@ -2256,7 +2263,7 @@
       <c r="F61" s="4">
         <v>110</v>
       </c>
-      <c r="G61" s="13">
+      <c r="G61" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H61" s="19">
@@ -2282,7 +2289,7 @@
       <c r="F62" s="4">
         <v>51</v>
       </c>
-      <c r="G62" s="13">
+      <c r="G62" s="18">
         <v>2.84</v>
       </c>
       <c r="H62" s="19">
@@ -2308,7 +2315,7 @@
       <c r="F63" s="4">
         <v>52</v>
       </c>
-      <c r="G63" s="13">
+      <c r="G63" s="18">
         <v>1.77</v>
       </c>
       <c r="H63" s="19">
@@ -2334,7 +2341,7 @@
       <c r="F64" s="4">
         <v>28</v>
       </c>
-      <c r="G64" s="13">
+      <c r="G64" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H64" s="19">
@@ -2360,7 +2367,7 @@
       <c r="F65" s="4">
         <v>136</v>
       </c>
-      <c r="G65" s="13">
+      <c r="G65" s="18">
         <v>1.77</v>
       </c>
       <c r="H65" s="19">
@@ -2386,7 +2393,7 @@
       <c r="F66" s="4">
         <v>42</v>
       </c>
-      <c r="G66" s="13">
+      <c r="G66" s="18">
         <v>3.49</v>
       </c>
       <c r="H66" s="19">
@@ -2412,7 +2419,7 @@
       <c r="F67" s="4">
         <v>75</v>
       </c>
-      <c r="G67" s="13">
+      <c r="G67" s="18">
         <v>1.87</v>
       </c>
       <c r="H67" s="19">
@@ -2438,7 +2445,7 @@
       <c r="F68" s="4">
         <v>72</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G68" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H68" s="19">
@@ -2464,7 +2471,7 @@
       <c r="F69" s="4">
         <v>56</v>
       </c>
-      <c r="G69" s="13">
+      <c r="G69" s="18">
         <v>2.84</v>
       </c>
       <c r="H69" s="19">
@@ -2490,7 +2497,7 @@
       <c r="F70" s="4">
         <v>51</v>
       </c>
-      <c r="G70" s="13">
+      <c r="G70" s="18">
         <v>1.87</v>
       </c>
       <c r="H70" s="19">
@@ -2516,7 +2523,7 @@
       <c r="F71" s="4">
         <v>31</v>
       </c>
-      <c r="G71" s="13">
+      <c r="G71" s="18">
         <v>1.68</v>
       </c>
       <c r="H71" s="19">
@@ -2542,7 +2549,7 @@
       <c r="F72" s="4">
         <v>56</v>
       </c>
-      <c r="G72" s="13">
+      <c r="G72" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H72" s="19">
@@ -2568,7 +2575,7 @@
       <c r="F73" s="4">
         <v>137</v>
       </c>
-      <c r="G73" s="13">
+      <c r="G73" s="18">
         <v>2.84</v>
       </c>
       <c r="H73" s="19">
@@ -2594,7 +2601,7 @@
       <c r="F74" s="4">
         <v>107</v>
       </c>
-      <c r="G74" s="13">
+      <c r="G74" s="18">
         <v>1.87</v>
       </c>
       <c r="H74" s="19">
@@ -2620,7 +2627,7 @@
       <c r="F75" s="4">
         <v>24</v>
       </c>
-      <c r="G75" s="13">
+      <c r="G75" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H75" s="19">
@@ -2646,7 +2653,7 @@
       <c r="F76" s="4">
         <v>30</v>
       </c>
-      <c r="G76" s="13">
+      <c r="G76" s="18">
         <v>3.49</v>
       </c>
       <c r="H76" s="19">
@@ -2672,7 +2679,7 @@
       <c r="F77" s="4">
         <v>70</v>
       </c>
-      <c r="G77" s="13">
+      <c r="G77" s="18">
         <v>1.87</v>
       </c>
       <c r="H77" s="19">
@@ -2698,7 +2705,7 @@
       <c r="F78" s="4">
         <v>31</v>
       </c>
-      <c r="G78" s="13">
+      <c r="G78" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H78" s="19">
@@ -2724,7 +2731,7 @@
       <c r="F79" s="4">
         <v>109</v>
       </c>
-      <c r="G79" s="13">
+      <c r="G79" s="18">
         <v>1.77</v>
       </c>
       <c r="H79" s="19">
@@ -2750,7 +2757,7 @@
       <c r="F80" s="4">
         <v>21</v>
       </c>
-      <c r="G80" s="13">
+      <c r="G80" s="18">
         <v>3.49</v>
       </c>
       <c r="H80" s="19">
@@ -2776,7 +2783,7 @@
       <c r="F81" s="4">
         <v>80</v>
       </c>
-      <c r="G81" s="13">
+      <c r="G81" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H81" s="19">
@@ -2802,7 +2809,7 @@
       <c r="F82" s="4">
         <v>75</v>
       </c>
-      <c r="G82" s="13">
+      <c r="G82" s="18">
         <v>1.87</v>
       </c>
       <c r="H82" s="19">
@@ -2828,7 +2835,7 @@
       <c r="F83" s="4">
         <v>74</v>
       </c>
-      <c r="G83" s="13">
+      <c r="G83" s="18">
         <v>2.84</v>
       </c>
       <c r="H83" s="19">
@@ -2854,7 +2861,7 @@
       <c r="F84" s="4">
         <v>45</v>
       </c>
-      <c r="G84" s="13">
+      <c r="G84" s="18">
         <v>1.77</v>
       </c>
       <c r="H84" s="19">
@@ -2880,7 +2887,7 @@
       <c r="F85" s="4">
         <v>28</v>
       </c>
-      <c r="G85" s="13">
+      <c r="G85" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H85" s="19">
@@ -2906,7 +2913,7 @@
       <c r="F86" s="4">
         <v>143</v>
       </c>
-      <c r="G86" s="13">
+      <c r="G86" s="18">
         <v>1.77</v>
       </c>
       <c r="H86" s="19">
@@ -2932,7 +2939,7 @@
       <c r="F87" s="4">
         <v>27</v>
       </c>
-      <c r="G87" s="13">
+      <c r="G87" s="18">
         <v>3.15</v>
       </c>
       <c r="H87" s="19">
@@ -2958,7 +2965,7 @@
       <c r="F88" s="4">
         <v>133</v>
       </c>
-      <c r="G88" s="13">
+      <c r="G88" s="18">
         <v>1.77</v>
       </c>
       <c r="H88" s="19">
@@ -2984,7 +2991,7 @@
       <c r="F89" s="4">
         <v>110</v>
       </c>
-      <c r="G89" s="13">
+      <c r="G89" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H89" s="19">
@@ -3010,7 +3017,7 @@
       <c r="F90" s="4">
         <v>65</v>
       </c>
-      <c r="G90" s="13">
+      <c r="G90" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H90" s="19">
@@ -3036,7 +3043,7 @@
       <c r="F91" s="4">
         <v>33</v>
       </c>
-      <c r="G91" s="13">
+      <c r="G91" s="18">
         <v>1.87</v>
       </c>
       <c r="H91" s="19">
@@ -3062,7 +3069,7 @@
       <c r="F92" s="4">
         <v>81</v>
       </c>
-      <c r="G92" s="13">
+      <c r="G92" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H92" s="19">
@@ -3088,7 +3095,7 @@
       <c r="F93" s="4">
         <v>77</v>
       </c>
-      <c r="G93" s="13">
+      <c r="G93" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H93" s="19">
@@ -3114,7 +3121,7 @@
       <c r="F94" s="4">
         <v>38</v>
       </c>
-      <c r="G94" s="13">
+      <c r="G94" s="18">
         <v>3.49</v>
       </c>
       <c r="H94" s="19">
@@ -3140,7 +3147,7 @@
       <c r="F95" s="4">
         <v>40</v>
       </c>
-      <c r="G95" s="13">
+      <c r="G95" s="18">
         <v>1.77</v>
       </c>
       <c r="H95" s="19">
@@ -3166,7 +3173,7 @@
       <c r="F96" s="4">
         <v>114</v>
       </c>
-      <c r="G96" s="13">
+      <c r="G96" s="18">
         <v>1.6800000000000002</v>
       </c>
       <c r="H96" s="19">
@@ -3192,7 +3199,7 @@
       <c r="F97" s="4">
         <v>224</v>
       </c>
-      <c r="G97" s="13">
+      <c r="G97" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H97" s="19">
@@ -3218,7 +3225,7 @@
       <c r="F98" s="4">
         <v>141</v>
       </c>
-      <c r="G98" s="13">
+      <c r="G98" s="18">
         <v>1.77</v>
       </c>
       <c r="H98" s="19">
@@ -3244,7 +3251,7 @@
       <c r="F99" s="4">
         <v>32</v>
       </c>
-      <c r="G99" s="13">
+      <c r="G99" s="18">
         <v>3.49</v>
       </c>
       <c r="H99" s="19">
@@ -3270,7 +3277,7 @@
       <c r="F100" s="4">
         <v>20</v>
       </c>
-      <c r="G100" s="13">
+      <c r="G100" s="18">
         <v>1.77</v>
       </c>
       <c r="H100" s="19">
@@ -3296,7 +3303,7 @@
       <c r="F101" s="4">
         <v>40</v>
       </c>
-      <c r="G101" s="13">
+      <c r="G101" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H101" s="19">
@@ -3322,7 +3329,7 @@
       <c r="F102" s="4">
         <v>49</v>
       </c>
-      <c r="G102" s="13">
+      <c r="G102" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H102" s="19">
@@ -3348,7 +3355,7 @@
       <c r="F103" s="4">
         <v>46</v>
       </c>
-      <c r="G103" s="13">
+      <c r="G103" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H103" s="19">
@@ -3374,7 +3381,7 @@
       <c r="F104" s="4">
         <v>39</v>
       </c>
-      <c r="G104" s="13">
+      <c r="G104" s="18">
         <v>1.77</v>
       </c>
       <c r="H104" s="19">
@@ -3400,7 +3407,7 @@
       <c r="F105" s="4">
         <v>62</v>
       </c>
-      <c r="G105" s="13">
+      <c r="G105" s="18">
         <v>1.68</v>
       </c>
       <c r="H105" s="19">
@@ -3426,7 +3433,7 @@
       <c r="F106" s="4">
         <v>90</v>
       </c>
-      <c r="G106" s="13">
+      <c r="G106" s="18">
         <v>1.77</v>
       </c>
       <c r="H106" s="19">
@@ -3452,7 +3459,7 @@
       <c r="F107" s="4">
         <v>103</v>
       </c>
-      <c r="G107" s="13">
+      <c r="G107" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H107" s="19">
@@ -3478,7 +3485,7 @@
       <c r="F108" s="4">
         <v>32</v>
       </c>
-      <c r="G108" s="13">
+      <c r="G108" s="18">
         <v>2.84</v>
       </c>
       <c r="H108" s="19">
@@ -3504,7 +3511,7 @@
       <c r="F109" s="4">
         <v>66</v>
       </c>
-      <c r="G109" s="13">
+      <c r="G109" s="18">
         <v>1.87</v>
       </c>
       <c r="H109" s="19">
@@ -3530,7 +3537,7 @@
       <c r="F110" s="4">
         <v>97</v>
       </c>
-      <c r="G110" s="13">
+      <c r="G110" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H110" s="19">
@@ -3556,7 +3563,7 @@
       <c r="F111" s="4">
         <v>30</v>
       </c>
-      <c r="G111" s="13">
+      <c r="G111" s="18">
         <v>1.77</v>
       </c>
       <c r="H111" s="19">
@@ -3582,7 +3589,7 @@
       <c r="F112" s="4">
         <v>29</v>
       </c>
-      <c r="G112" s="13">
+      <c r="G112" s="18">
         <v>1.68</v>
       </c>
       <c r="H112" s="19">
@@ -3608,7 +3615,7 @@
       <c r="F113" s="4">
         <v>92</v>
       </c>
-      <c r="G113" s="13">
+      <c r="G113" s="18">
         <v>1.77</v>
       </c>
       <c r="H113" s="19">
@@ -3634,7 +3641,7 @@
       <c r="F114" s="4">
         <v>139</v>
       </c>
-      <c r="G114" s="13">
+      <c r="G114" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H114" s="19">
@@ -3660,7 +3667,7 @@
       <c r="F115" s="4">
         <v>29</v>
       </c>
-      <c r="G115" s="13">
+      <c r="G115" s="18">
         <v>2.84</v>
       </c>
       <c r="H115" s="19">
@@ -3686,7 +3693,7 @@
       <c r="F116" s="4">
         <v>30</v>
       </c>
-      <c r="G116" s="13">
+      <c r="G116" s="18">
         <v>2.27</v>
       </c>
       <c r="H116" s="19">
@@ -3712,7 +3719,7 @@
       <c r="F117" s="4">
         <v>36</v>
       </c>
-      <c r="G117" s="13">
+      <c r="G117" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H117" s="19">
@@ -3738,7 +3745,7 @@
       <c r="F118" s="4">
         <v>41</v>
       </c>
-      <c r="G118" s="13">
+      <c r="G118" s="18">
         <v>3.49</v>
       </c>
       <c r="H118" s="19">
@@ -3764,7 +3771,7 @@
       <c r="F119" s="4">
         <v>44</v>
       </c>
-      <c r="G119" s="13">
+      <c r="G119" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H119" s="19">
@@ -3790,7 +3797,7 @@
       <c r="F120" s="4">
         <v>29</v>
       </c>
-      <c r="G120" s="13">
+      <c r="G120" s="18">
         <v>1.68</v>
       </c>
       <c r="H120" s="19">
@@ -3816,7 +3823,7 @@
       <c r="F121" s="4">
         <v>237</v>
       </c>
-      <c r="G121" s="13">
+      <c r="G121" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H121" s="19">
@@ -3842,7 +3849,7 @@
       <c r="F122" s="4">
         <v>65</v>
       </c>
-      <c r="G122" s="13">
+      <c r="G122" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H122" s="19">
@@ -3868,7 +3875,7 @@
       <c r="F123" s="4">
         <v>83</v>
       </c>
-      <c r="G123" s="13">
+      <c r="G123" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H123" s="19">
@@ -3894,7 +3901,7 @@
       <c r="F124" s="4">
         <v>32</v>
       </c>
-      <c r="G124" s="13">
+      <c r="G124" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H124" s="19">
@@ -3920,7 +3927,7 @@
       <c r="F125" s="4">
         <v>63</v>
       </c>
-      <c r="G125" s="13">
+      <c r="G125" s="18">
         <v>1.77</v>
       </c>
       <c r="H125" s="19">
@@ -3946,7 +3953,7 @@
       <c r="F126" s="4">
         <v>29</v>
       </c>
-      <c r="G126" s="13">
+      <c r="G126" s="18">
         <v>3.15</v>
       </c>
       <c r="H126" s="19">
@@ -3972,7 +3979,7 @@
       <c r="F127" s="4">
         <v>77</v>
       </c>
-      <c r="G127" s="13">
+      <c r="G127" s="18">
         <v>1.87</v>
       </c>
       <c r="H127" s="19">
@@ -3998,7 +4005,7 @@
       <c r="F128" s="4">
         <v>80</v>
       </c>
-      <c r="G128" s="13">
+      <c r="G128" s="18">
         <v>2.84</v>
       </c>
       <c r="H128" s="19">
@@ -4024,7 +4031,7 @@
       <c r="F129" s="4">
         <v>102</v>
       </c>
-      <c r="G129" s="13">
+      <c r="G129" s="18">
         <v>1.77</v>
       </c>
       <c r="H129" s="19">
@@ -4050,7 +4057,7 @@
       <c r="F130" s="4">
         <v>31</v>
       </c>
-      <c r="G130" s="13">
+      <c r="G130" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H130" s="19">
@@ -4076,7 +4083,7 @@
       <c r="F131" s="4">
         <v>56</v>
       </c>
-      <c r="G131" s="13">
+      <c r="G131" s="18">
         <v>1.77</v>
       </c>
       <c r="H131" s="19">
@@ -4102,7 +4109,7 @@
       <c r="F132" s="4">
         <v>52</v>
       </c>
-      <c r="G132" s="13">
+      <c r="G132" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H132" s="19">
@@ -4128,7 +4135,7 @@
       <c r="F133" s="4">
         <v>51</v>
       </c>
-      <c r="G133" s="13">
+      <c r="G133" s="18">
         <v>1.77</v>
       </c>
       <c r="H133" s="19">
@@ -4154,7 +4161,7 @@
       <c r="F134" s="4">
         <v>24</v>
       </c>
-      <c r="G134" s="13">
+      <c r="G134" s="18">
         <v>1.68</v>
       </c>
       <c r="H134" s="19">
@@ -4180,7 +4187,7 @@
       <c r="F135" s="4">
         <v>58</v>
       </c>
-      <c r="G135" s="13">
+      <c r="G135" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H135" s="19">
@@ -4206,7 +4213,7 @@
       <c r="F136" s="4">
         <v>34</v>
       </c>
-      <c r="G136" s="13">
+      <c r="G136" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H136" s="19">
@@ -4232,7 +4239,7 @@
       <c r="F137" s="4">
         <v>34</v>
       </c>
-      <c r="G137" s="13">
+      <c r="G137" s="18">
         <v>1.77</v>
       </c>
       <c r="H137" s="19">
@@ -4258,7 +4265,7 @@
       <c r="F138" s="4">
         <v>21</v>
       </c>
-      <c r="G138" s="13">
+      <c r="G138" s="18">
         <v>1.6800000000000002</v>
       </c>
       <c r="H138" s="19">
@@ -4284,7 +4291,7 @@
       <c r="F139" s="4">
         <v>29</v>
       </c>
-      <c r="G139" s="13">
+      <c r="G139" s="18">
         <v>2.84</v>
       </c>
       <c r="H139" s="19">
@@ -4310,7 +4317,7 @@
       <c r="F140" s="4">
         <v>68</v>
       </c>
-      <c r="G140" s="13">
+      <c r="G140" s="18">
         <v>1.77</v>
       </c>
       <c r="H140" s="19">
@@ -4336,7 +4343,7 @@
       <c r="F141" s="4">
         <v>31</v>
       </c>
-      <c r="G141" s="13">
+      <c r="G141" s="18">
         <v>3.1500000000000004</v>
       </c>
       <c r="H141" s="19">
@@ -4362,7 +4369,7 @@
       <c r="F142" s="4">
         <v>30</v>
       </c>
-      <c r="G142" s="13">
+      <c r="G142" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H142" s="19">
@@ -4388,7 +4395,7 @@
       <c r="F143" s="4">
         <v>232</v>
       </c>
-      <c r="G143" s="13">
+      <c r="G143" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H143" s="19">
@@ -4414,7 +4421,7 @@
       <c r="F144" s="4">
         <v>68</v>
       </c>
-      <c r="G144" s="13">
+      <c r="G144" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H144" s="19">
@@ -4440,7 +4447,7 @@
       <c r="F145" s="4">
         <v>97</v>
       </c>
-      <c r="G145" s="13">
+      <c r="G145" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H145" s="19">
@@ -4466,7 +4473,7 @@
       <c r="F146" s="4">
         <v>86</v>
       </c>
-      <c r="G146" s="13">
+      <c r="G146" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H146" s="19">
@@ -4492,7 +4499,7 @@
       <c r="F147" s="4">
         <v>41</v>
       </c>
-      <c r="G147" s="13">
+      <c r="G147" s="18">
         <v>1.68</v>
       </c>
       <c r="H147" s="19">
@@ -4518,7 +4525,7 @@
       <c r="F148" s="4">
         <v>93</v>
       </c>
-      <c r="G148" s="13">
+      <c r="G148" s="18">
         <v>1.7700000000000002</v>
       </c>
       <c r="H148" s="19">
@@ -4544,7 +4551,7 @@
       <c r="F149" s="4">
         <v>47</v>
       </c>
-      <c r="G149" s="13">
+      <c r="G149" s="18">
         <v>1.68</v>
       </c>
       <c r="H149" s="19">
@@ -4570,7 +4577,7 @@
       <c r="F150" s="4">
         <v>103</v>
       </c>
-      <c r="G150" s="13">
+      <c r="G150" s="18">
         <v>1.77</v>
       </c>
       <c r="H150" s="19">
@@ -4596,7 +4603,7 @@
       <c r="F151" s="4">
         <v>33</v>
       </c>
-      <c r="G151" s="13">
+      <c r="G151" s="18">
         <v>1.68</v>
       </c>
       <c r="H151" s="19">
@@ -4622,7 +4629,7 @@
       <c r="F152" s="4">
         <v>57</v>
       </c>
-      <c r="G152" s="13">
+      <c r="G152" s="18">
         <v>1.87</v>
       </c>
       <c r="H152" s="19">
@@ -4648,7 +4655,7 @@
       <c r="F153" s="4">
         <v>65</v>
       </c>
-      <c r="G153" s="13">
+      <c r="G153" s="18">
         <v>2.84</v>
       </c>
       <c r="H153" s="19">
@@ -4674,7 +4681,7 @@
       <c r="F154" s="4">
         <v>118</v>
       </c>
-      <c r="G154" s="13">
+      <c r="G154" s="18">
         <v>1.77</v>
       </c>
       <c r="H154" s="19">
@@ -4700,7 +4707,7 @@
       <c r="F155" s="4">
         <v>36</v>
       </c>
-      <c r="G155" s="13">
+      <c r="G155" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H155" s="19">
@@ -4726,7 +4733,7 @@
       <c r="F156" s="4">
         <v>123</v>
       </c>
-      <c r="G156" s="13">
+      <c r="G156" s="18">
         <v>2.84</v>
       </c>
       <c r="H156" s="19">
@@ -4752,7 +4759,7 @@
       <c r="F157" s="4">
         <v>90</v>
       </c>
-      <c r="G157" s="13">
+      <c r="G157" s="18">
         <v>1.77</v>
       </c>
       <c r="H157" s="19">
@@ -4778,7 +4785,7 @@
       <c r="F158" s="4">
         <v>21</v>
       </c>
-      <c r="G158" s="13">
+      <c r="G158" s="18">
         <v>3.49</v>
       </c>
       <c r="H158" s="19">
@@ -4804,7 +4811,7 @@
       <c r="F159" s="4">
         <v>48</v>
       </c>
-      <c r="G159" s="13">
+      <c r="G159" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H159" s="19">
@@ -4830,7 +4837,7 @@
       <c r="F160" s="4">
         <v>24</v>
       </c>
-      <c r="G160" s="13">
+      <c r="G160" s="18">
         <v>1.68</v>
       </c>
       <c r="H160" s="19">
@@ -4856,7 +4863,7 @@
       <c r="F161" s="4">
         <v>67</v>
       </c>
-      <c r="G161" s="13">
+      <c r="G161" s="18">
         <v>1.87</v>
       </c>
       <c r="H161" s="19">
@@ -4882,7 +4889,7 @@
       <c r="F162" s="4">
         <v>27</v>
       </c>
-      <c r="G162" s="13">
+      <c r="G162" s="18">
         <v>1.87</v>
       </c>
       <c r="H162" s="19">
@@ -4908,7 +4915,7 @@
       <c r="F163" s="4">
         <v>129</v>
       </c>
-      <c r="G163" s="13">
+      <c r="G163" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H163" s="19">
@@ -4934,7 +4941,7 @@
       <c r="F164" s="4">
         <v>77</v>
       </c>
-      <c r="G164" s="13">
+      <c r="G164" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H164" s="19">
@@ -4960,7 +4967,7 @@
       <c r="F165" s="4">
         <v>58</v>
       </c>
-      <c r="G165" s="13">
+      <c r="G165" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H165" s="19">
@@ -4986,7 +4993,7 @@
       <c r="F166" s="4">
         <v>47</v>
       </c>
-      <c r="G166" s="13">
+      <c r="G166" s="18">
         <v>1.87</v>
       </c>
       <c r="H166" s="19">
@@ -5012,7 +5019,7 @@
       <c r="F167" s="4">
         <v>33</v>
       </c>
-      <c r="G167" s="13">
+      <c r="G167" s="18">
         <v>2.84</v>
       </c>
       <c r="H167" s="19">
@@ -5038,7 +5045,7 @@
       <c r="F168" s="4">
         <v>82</v>
       </c>
-      <c r="G168" s="13">
+      <c r="G168" s="18">
         <v>1.87</v>
       </c>
       <c r="H168" s="19">
@@ -5064,7 +5071,7 @@
       <c r="F169" s="4">
         <v>58</v>
       </c>
-      <c r="G169" s="13">
+      <c r="G169" s="18">
         <v>1.77</v>
       </c>
       <c r="H169" s="19">
@@ -5090,7 +5097,7 @@
       <c r="F170" s="4">
         <v>30</v>
       </c>
-      <c r="G170" s="13">
+      <c r="G170" s="18">
         <v>3.15</v>
       </c>
       <c r="H170" s="19">
@@ -5116,7 +5123,7 @@
       <c r="F171" s="4">
         <v>43</v>
       </c>
-      <c r="G171" s="13">
+      <c r="G171" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H171" s="19">
@@ -5142,7 +5149,7 @@
       <c r="F172" s="4">
         <v>84</v>
       </c>
-      <c r="G172" s="13">
+      <c r="G172" s="18">
         <v>1.77</v>
       </c>
       <c r="H172" s="19">
@@ -5168,7 +5175,7 @@
       <c r="F173" s="4">
         <v>36</v>
       </c>
-      <c r="G173" s="13">
+      <c r="G173" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H173" s="19">
@@ -5194,7 +5201,7 @@
       <c r="F174" s="4">
         <v>44</v>
       </c>
-      <c r="G174" s="13">
+      <c r="G174" s="18">
         <v>2.84</v>
       </c>
       <c r="H174" s="19">
@@ -5220,7 +5227,7 @@
       <c r="F175" s="4">
         <v>27</v>
       </c>
-      <c r="G175" s="13">
+      <c r="G175" s="18">
         <v>1.87</v>
       </c>
       <c r="H175" s="19">
@@ -5246,7 +5253,7 @@
       <c r="F176" s="4">
         <v>120</v>
       </c>
-      <c r="G176" s="13">
+      <c r="G176" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H176" s="19">
@@ -5272,7 +5279,7 @@
       <c r="F177" s="4">
         <v>26</v>
       </c>
-      <c r="G177" s="13">
+      <c r="G177" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H177" s="19">
@@ -5298,7 +5305,7 @@
       <c r="F178" s="4">
         <v>73</v>
       </c>
-      <c r="G178" s="13">
+      <c r="G178" s="18">
         <v>1.77</v>
       </c>
       <c r="H178" s="19">
@@ -5324,7 +5331,7 @@
       <c r="F179" s="4">
         <v>38</v>
       </c>
-      <c r="G179" s="13">
+      <c r="G179" s="18">
         <v>1.87</v>
       </c>
       <c r="H179" s="19">
@@ -5350,7 +5357,7 @@
       <c r="F180" s="4">
         <v>40</v>
       </c>
-      <c r="G180" s="13">
+      <c r="G180" s="18">
         <v>2.84</v>
       </c>
       <c r="H180" s="19">
@@ -5376,7 +5383,7 @@
       <c r="F181" s="4">
         <v>41</v>
       </c>
-      <c r="G181" s="13">
+      <c r="G181" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H181" s="19">
@@ -5402,7 +5409,7 @@
       <c r="F182" s="4">
         <v>27</v>
       </c>
-      <c r="G182" s="13">
+      <c r="G182" s="18">
         <v>2.27</v>
       </c>
       <c r="H182" s="19">
@@ -5428,7 +5435,7 @@
       <c r="F183" s="4">
         <v>38</v>
       </c>
-      <c r="G183" s="13">
+      <c r="G183" s="18">
         <v>1.87</v>
       </c>
       <c r="H183" s="19">
@@ -5454,7 +5461,7 @@
       <c r="F184" s="4">
         <v>34</v>
       </c>
-      <c r="G184" s="13">
+      <c r="G184" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H184" s="19">
@@ -5480,7 +5487,7 @@
       <c r="F185" s="4">
         <v>65</v>
       </c>
-      <c r="G185" s="13">
+      <c r="G185" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H185" s="19">
@@ -5506,7 +5513,7 @@
       <c r="F186" s="4">
         <v>60</v>
       </c>
-      <c r="G186" s="13">
+      <c r="G186" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H186" s="19">
@@ -5532,7 +5539,7 @@
       <c r="F187" s="4">
         <v>37</v>
       </c>
-      <c r="G187" s="13">
+      <c r="G187" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H187" s="19">
@@ -5558,7 +5565,7 @@
       <c r="F188" s="4">
         <v>40</v>
       </c>
-      <c r="G188" s="13">
+      <c r="G188" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H188" s="19">
@@ -5584,7 +5591,7 @@
       <c r="F189" s="4">
         <v>26</v>
       </c>
-      <c r="G189" s="13">
+      <c r="G189" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H189" s="19">
@@ -5610,7 +5617,7 @@
       <c r="F190" s="4">
         <v>22</v>
       </c>
-      <c r="G190" s="13">
+      <c r="G190" s="18">
         <v>2.27</v>
       </c>
       <c r="H190" s="19">
@@ -5636,7 +5643,7 @@
       <c r="F191" s="4">
         <v>32</v>
       </c>
-      <c r="G191" s="13">
+      <c r="G191" s="18">
         <v>1.87</v>
       </c>
       <c r="H191" s="19">
@@ -5662,7 +5669,7 @@
       <c r="F192" s="4">
         <v>23</v>
       </c>
-      <c r="G192" s="13">
+      <c r="G192" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H192" s="19">
@@ -5688,7 +5695,7 @@
       <c r="F193" s="4">
         <v>20</v>
       </c>
-      <c r="G193" s="13">
+      <c r="G193" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H193" s="19">
@@ -5714,7 +5721,7 @@
       <c r="F194" s="4">
         <v>64</v>
       </c>
-      <c r="G194" s="13">
+      <c r="G194" s="18">
         <v>1.87</v>
       </c>
       <c r="H194" s="19">
@@ -5740,7 +5747,7 @@
       <c r="F195" s="4">
         <v>71</v>
       </c>
-      <c r="G195" s="13">
+      <c r="G195" s="18">
         <v>1.77</v>
       </c>
       <c r="H195" s="19">
@@ -5766,7 +5773,7 @@
       <c r="F196" s="4">
         <v>90</v>
       </c>
-      <c r="G196" s="13">
+      <c r="G196" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H196" s="19">
@@ -5792,7 +5799,7 @@
       <c r="F197" s="4">
         <v>38</v>
       </c>
-      <c r="G197" s="13">
+      <c r="G197" s="18">
         <v>2.84</v>
       </c>
       <c r="H197" s="19">
@@ -5818,7 +5825,7 @@
       <c r="F198" s="4">
         <v>55</v>
       </c>
-      <c r="G198" s="13">
+      <c r="G198" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H198" s="19">
@@ -5844,7 +5851,7 @@
       <c r="F199" s="4">
         <v>22</v>
       </c>
-      <c r="G199" s="13">
+      <c r="G199" s="18">
         <v>3.15</v>
       </c>
       <c r="H199" s="19">
@@ -5870,7 +5877,7 @@
       <c r="F200" s="4">
         <v>34</v>
       </c>
-      <c r="G200" s="13">
+      <c r="G200" s="18">
         <v>1.77</v>
       </c>
       <c r="H200" s="19">
@@ -5896,7 +5903,7 @@
       <c r="F201" s="4">
         <v>39</v>
       </c>
-      <c r="G201" s="13">
+      <c r="G201" s="18">
         <v>1.87</v>
       </c>
       <c r="H201" s="19">
@@ -5922,7 +5929,7 @@
       <c r="F202" s="4">
         <v>41</v>
       </c>
-      <c r="G202" s="13">
+      <c r="G202" s="18">
         <v>2.84</v>
       </c>
       <c r="H202" s="19">
@@ -5948,7 +5955,7 @@
       <c r="F203" s="4">
         <v>41</v>
       </c>
-      <c r="G203" s="13">
+      <c r="G203" s="18">
         <v>1.7699999999999998</v>
       </c>
       <c r="H203" s="19">
@@ -5974,7 +5981,7 @@
       <c r="F204" s="4">
         <v>136</v>
       </c>
-      <c r="G204" s="13">
+      <c r="G204" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H204" s="19">
@@ -6000,7 +6007,7 @@
       <c r="F205" s="4">
         <v>25</v>
       </c>
-      <c r="G205" s="13">
+      <c r="G205" s="18">
         <v>1.77</v>
       </c>
       <c r="H205" s="19">
@@ -6026,7 +6033,7 @@
       <c r="F206" s="4">
         <v>26</v>
       </c>
-      <c r="G206" s="13">
+      <c r="G206" s="18">
         <v>3.1500000000000004</v>
       </c>
       <c r="H206" s="19">
@@ -6052,7 +6059,7 @@
       <c r="F207" s="4">
         <v>50</v>
       </c>
-      <c r="G207" s="13">
+      <c r="G207" s="18">
         <v>1.87</v>
       </c>
       <c r="H207" s="19">
@@ -6078,7 +6085,7 @@
       <c r="F208" s="4">
         <v>79</v>
       </c>
-      <c r="G208" s="13">
+      <c r="G208" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H208" s="19">
@@ -6104,7 +6111,7 @@
       <c r="F209" s="4">
         <v>30</v>
       </c>
-      <c r="G209" s="13">
+      <c r="G209" s="18">
         <v>1.77</v>
       </c>
       <c r="H209" s="19">
@@ -6130,7 +6137,7 @@
       <c r="F210" s="4">
         <v>20</v>
       </c>
-      <c r="G210" s="13">
+      <c r="G210" s="18">
         <v>1.6800000000000002</v>
       </c>
       <c r="H210" s="19">
@@ -6156,7 +6163,7 @@
       <c r="F211" s="4">
         <v>49</v>
       </c>
-      <c r="G211" s="13">
+      <c r="G211" s="18">
         <v>1.77</v>
       </c>
       <c r="H211" s="19">
@@ -6182,7 +6189,7 @@
       <c r="F212" s="4">
         <v>40</v>
       </c>
-      <c r="G212" s="13">
+      <c r="G212" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H212" s="19">
@@ -6208,7 +6215,7 @@
       <c r="F213" s="4">
         <v>31</v>
       </c>
-      <c r="G213" s="13">
+      <c r="G213" s="18">
         <v>1.77</v>
       </c>
       <c r="H213" s="19">
@@ -6234,7 +6241,7 @@
       <c r="F214" s="4">
         <v>21</v>
       </c>
-      <c r="G214" s="13">
+      <c r="G214" s="18">
         <v>3.1500000000000004</v>
       </c>
       <c r="H214" s="19">
@@ -6260,7 +6267,7 @@
       <c r="F215" s="4">
         <v>43</v>
       </c>
-      <c r="G215" s="13">
+      <c r="G215" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H215" s="19">
@@ -6286,7 +6293,7 @@
       <c r="F216" s="4">
         <v>47</v>
       </c>
-      <c r="G216" s="13">
+      <c r="G216" s="18">
         <v>2.84</v>
       </c>
       <c r="H216" s="19">
@@ -6312,7 +6319,7 @@
       <c r="F217" s="4">
         <v>175</v>
       </c>
-      <c r="G217" s="13">
+      <c r="G217" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H217" s="19">
@@ -6338,7 +6345,7 @@
       <c r="F218" s="4">
         <v>23</v>
       </c>
-      <c r="G218" s="13">
+      <c r="G218" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H218" s="19">
@@ -6364,7 +6371,7 @@
       <c r="F219" s="4">
         <v>40</v>
       </c>
-      <c r="G219" s="13">
+      <c r="G219" s="18">
         <v>1.77</v>
       </c>
       <c r="H219" s="19">
@@ -6390,7 +6397,7 @@
       <c r="F220" s="4">
         <v>87</v>
       </c>
-      <c r="G220" s="13">
+      <c r="G220" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H220" s="19">
@@ -6416,7 +6423,7 @@
       <c r="F221" s="4">
         <v>43</v>
       </c>
-      <c r="G221" s="13">
+      <c r="G221" s="18">
         <v>1.77</v>
       </c>
       <c r="H221" s="19">
@@ -6442,7 +6449,7 @@
       <c r="F222" s="4">
         <v>30</v>
       </c>
-      <c r="G222" s="13">
+      <c r="G222" s="18">
         <v>3.49</v>
       </c>
       <c r="H222" s="19">
@@ -6468,7 +6475,7 @@
       <c r="F223" s="4">
         <v>35</v>
       </c>
-      <c r="G223" s="13">
+      <c r="G223" s="18">
         <v>1.77</v>
       </c>
       <c r="H223" s="19">
@@ -6494,7 +6501,7 @@
       <c r="F224" s="4">
         <v>57</v>
       </c>
-      <c r="G224" s="13">
+      <c r="G224" s="18">
         <v>1.87</v>
       </c>
       <c r="H224" s="19">
@@ -6520,7 +6527,7 @@
       <c r="F225" s="4">
         <v>25</v>
       </c>
-      <c r="G225" s="13">
+      <c r="G225" s="18">
         <v>1.68</v>
       </c>
       <c r="H225" s="19">
@@ -6546,7 +6553,7 @@
       <c r="F226" s="4">
         <v>24</v>
       </c>
-      <c r="G226" s="13">
+      <c r="G226" s="18">
         <v>1.87</v>
       </c>
       <c r="H226" s="19">
@@ -6572,7 +6579,7 @@
       <c r="F227" s="4">
         <v>83</v>
       </c>
-      <c r="G227" s="13">
+      <c r="G227" s="18">
         <v>1.87</v>
       </c>
       <c r="H227" s="19">
@@ -6598,7 +6605,7 @@
       <c r="F228" s="4">
         <v>124</v>
       </c>
-      <c r="G228" s="13">
+      <c r="G228" s="18">
         <v>2.8400000000000003</v>
       </c>
       <c r="H228" s="19">
@@ -6624,7 +6631,7 @@
       <c r="F229" s="4">
         <v>137</v>
       </c>
-      <c r="G229" s="13">
+      <c r="G229" s="18">
         <v>1.77</v>
       </c>
       <c r="H229" s="19">
@@ -6650,7 +6657,7 @@
       <c r="F230" s="4">
         <v>146</v>
       </c>
-      <c r="G230" s="13">
+      <c r="G230" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H230" s="19">
@@ -6676,7 +6683,7 @@
       <c r="F231" s="4">
         <v>34</v>
       </c>
-      <c r="G231" s="13">
+      <c r="G231" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H231" s="19">
@@ -6702,7 +6709,7 @@
       <c r="F232" s="4">
         <v>20</v>
       </c>
-      <c r="G232" s="13">
+      <c r="G232" s="18">
         <v>1.77</v>
       </c>
       <c r="H232" s="19">
@@ -6728,7 +6735,7 @@
       <c r="F233" s="4">
         <v>139</v>
       </c>
-      <c r="G233" s="13">
+      <c r="G233" s="18">
         <v>2.1799999999999997</v>
       </c>
       <c r="H233" s="19">
@@ -6754,7 +6761,7 @@
       <c r="F234" s="4">
         <v>211</v>
       </c>
-      <c r="G234" s="13">
+      <c r="G234" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H234" s="19">
@@ -6780,7 +6787,7 @@
       <c r="F235" s="4">
         <v>20</v>
       </c>
-      <c r="G235" s="13">
+      <c r="G235" s="18">
         <v>3.4899999999999998</v>
       </c>
       <c r="H235" s="19">
@@ -6806,7 +6813,7 @@
       <c r="F236" s="4">
         <v>42</v>
       </c>
-      <c r="G236" s="13">
+      <c r="G236" s="18">
         <v>1.87</v>
       </c>
       <c r="H236" s="19">
@@ -6832,7 +6839,7 @@
       <c r="F237" s="4">
         <v>100</v>
       </c>
-      <c r="G237" s="13">
+      <c r="G237" s="18">
         <v>2.84</v>
       </c>
       <c r="H237" s="19">
@@ -6858,7 +6865,7 @@
       <c r="F238" s="4">
         <v>38</v>
       </c>
-      <c r="G238" s="13">
+      <c r="G238" s="18">
         <v>1.7700000000000002</v>
       </c>
       <c r="H238" s="19">
@@ -6884,7 +6891,7 @@
       <c r="F239" s="4">
         <v>25</v>
       </c>
-      <c r="G239" s="13">
+      <c r="G239" s="18">
         <v>3.49</v>
       </c>
       <c r="H239" s="19">
@@ -6910,7 +6917,7 @@
       <c r="F240" s="4">
         <v>96</v>
       </c>
-      <c r="G240" s="13">
+      <c r="G240" s="18">
         <v>1.87</v>
       </c>
       <c r="H240" s="19">
@@ -6936,7 +6943,7 @@
       <c r="F241" s="4">
         <v>34</v>
       </c>
-      <c r="G241" s="13">
+      <c r="G241" s="18">
         <v>2.1800000000000002</v>
       </c>
       <c r="H241" s="19">
@@ -6962,7 +6969,7 @@
       <c r="F242" s="4">
         <v>245</v>
       </c>
-      <c r="G242" s="13">
+      <c r="G242" s="18">
         <v>1.8699999999999999</v>
       </c>
       <c r="H242" s="19">
@@ -6988,7 +6995,7 @@
       <c r="F243" s="4">
         <v>30</v>
       </c>
-      <c r="G243" s="13">
+      <c r="G243" s="18">
         <v>3.49</v>
       </c>
       <c r="H243" s="19">
@@ -7014,7 +7021,7 @@
       <c r="F244" s="4">
         <v>30</v>
       </c>
-      <c r="G244" s="13">
+      <c r="G244" s="18">
         <v>1.87</v>
       </c>
       <c r="H244" s="19">
@@ -7040,7 +7047,7 @@
       <c r="F245" s="4">
         <v>44</v>
       </c>
-      <c r="G245" s="13">
+      <c r="G245" s="18">
         <v>2.84</v>
       </c>
       <c r="H245" s="19">
@@ -7839,104 +7846,104 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="15">
         <v>0.82910733307190976</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="15">
         <v>0.7420603747872464</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="15">
         <v>0.81380912620137236</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="15">
         <v>0.79729717536552935</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="15">
         <v>0.64006397916607716</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <v>0.76606558679266601</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <v>0.63798856930470693</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="15">
         <v>0.61680151373759184</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <v>0.8516975277474973</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="15">
         <v>0.92684673282613694</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>0.62004659043636512</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="15">
         <v>0.91840057177855861</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <v>0.61324142503681667</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <v>0.92891939766567455</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>0.92845808610941249</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>0.74672643712491371</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>0.76348312206954005</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="15">
         <v>0.60145212273180249</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>0.79702549381767307</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="15">
         <v>0.67939804078485277</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>0.61638878759185434</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="15">
         <v>0.68031349142077857</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>0.90824533976520105</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="15">
         <v>0.89931136205624695</v>
       </c>
     </row>
@@ -8986,10 +8993,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="17">
+      <c r="A2" s="16">
         <v>100242</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <v>44198</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -9018,10 +9025,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="17">
+      <c r="A3" s="16">
         <v>100314</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>44198</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -9050,10 +9057,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="17">
+      <c r="A4" s="16">
         <v>100359</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>44198</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -9082,10 +9089,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="17">
+      <c r="A5" s="16">
         <v>100315</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>44199</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -9114,10 +9121,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="17">
+      <c r="A6" s="16">
         <v>100385</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>44199</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -9146,10 +9153,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="17">
+      <c r="A7" s="16">
         <v>100388</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>44200</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -9178,10 +9185,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="17">
+      <c r="A8" s="16">
         <v>100358</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>44201</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -9210,10 +9217,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="17">
+      <c r="A9" s="16">
         <v>100264</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <v>44203</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -9242,10 +9249,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="17">
+      <c r="A10" s="16">
         <v>100265</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <v>44203</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -9274,10 +9281,10 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="17">
+      <c r="A11" s="16">
         <v>100357</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <v>44204</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -9306,10 +9313,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17">
+      <c r="A12" s="16">
         <v>100399</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <v>44204</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -9338,10 +9345,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="17">
+      <c r="A13" s="16">
         <v>100329</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="17">
         <v>44205</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -9370,10 +9377,10 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="17">
+      <c r="A14" s="16">
         <v>100429</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>44205</v>
       </c>
       <c r="C14" s="8" t="s">
@@ -9402,10 +9409,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="17">
+      <c r="A15" s="16">
         <v>100441</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <v>44206</v>
       </c>
       <c r="C15" s="8" t="s">
@@ -9434,10 +9441,10 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="17">
+      <c r="A16" s="16">
         <v>100442</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>44206</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -9466,10 +9473,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="17">
+      <c r="A17" s="16">
         <v>100372</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="17">
         <v>44208</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -9498,10 +9505,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="17">
+      <c r="A18" s="16">
         <v>100281</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>44209</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -9530,10 +9537,10 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="17">
+      <c r="A19" s="16">
         <v>100280</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>44211</v>
       </c>
       <c r="C19" s="8" t="s">
@@ -9562,10 +9569,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="17">
+      <c r="A20" s="16">
         <v>100424</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>44212</v>
       </c>
       <c r="C20" s="8" t="s">
@@ -9594,10 +9601,10 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="17">
+      <c r="A21" s="16">
         <v>100425</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <v>44212</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -9626,10 +9633,10 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="17">
+      <c r="A22" s="16">
         <v>100426</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="17">
         <v>44212</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -9658,10 +9665,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="17">
+      <c r="A23" s="16">
         <v>100252</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="17">
         <v>44213</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -9690,10 +9697,10 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="17">
+      <c r="A24" s="16">
         <v>100279</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="17">
         <v>44214</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -9722,10 +9729,10 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="17">
+      <c r="A25" s="16">
         <v>100292</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="17">
         <v>44214</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -9754,10 +9761,10 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="17">
+      <c r="A26" s="16">
         <v>100398</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="17">
         <v>44214</v>
       </c>
       <c r="C26" s="8" t="s">
@@ -9786,10 +9793,10 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="17">
+      <c r="A27" s="16">
         <v>100382</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="17">
         <v>44215</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -9818,10 +9825,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="17">
+      <c r="A28" s="16">
         <v>100461</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="17">
         <v>44216</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -9850,10 +9857,10 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="17">
+      <c r="A29" s="16">
         <v>100263</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="17">
         <v>44218</v>
       </c>
       <c r="C29" s="8" t="s">
@@ -9882,10 +9889,10 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="17">
+      <c r="A30" s="16">
         <v>100453</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="17">
         <v>44218</v>
       </c>
       <c r="C30" s="8" t="s">
@@ -9914,10 +9921,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="17">
+      <c r="A31" s="16">
         <v>100381</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="17">
         <v>44219</v>
       </c>
       <c r="C31" s="8" t="s">
@@ -9946,10 +9953,10 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="17">
+      <c r="A32" s="16">
         <v>100275</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <v>44221</v>
       </c>
       <c r="C32" s="8" t="s">
@@ -9978,10 +9985,10 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="17">
+      <c r="A33" s="16">
         <v>100277</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="17">
         <v>44221</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -10010,10 +10017,10 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="17">
+      <c r="A34" s="16">
         <v>100312</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="17">
         <v>44221</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -10042,10 +10049,10 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="17">
+      <c r="A35" s="16">
         <v>100327</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="17">
         <v>44221</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -10074,10 +10081,10 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="17">
+      <c r="A36" s="16">
         <v>100326</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="17">
         <v>44222</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -10106,10 +10113,10 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="17">
+      <c r="A37" s="16">
         <v>100379</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="17">
         <v>44222</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -10138,10 +10145,10 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="17">
+      <c r="A38" s="16">
         <v>100310</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="17">
         <v>44224</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -10170,10 +10177,10 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="17">
+      <c r="A39" s="16">
         <v>100341</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="17">
         <v>44224</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -10202,10 +10209,10 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="17">
+      <c r="A40" s="16">
         <v>100289</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="17">
         <v>44225</v>
       </c>
       <c r="C40" s="8" t="s">
@@ -10234,10 +10241,10 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="17">
+      <c r="A41" s="16">
         <v>100290</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="17">
         <v>44225</v>
       </c>
       <c r="C41" s="8" t="s">
@@ -10266,10 +10273,10 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="17">
+      <c r="A42" s="16">
         <v>100291</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="17">
         <v>44225</v>
       </c>
       <c r="C42" s="8" t="s">
@@ -10298,10 +10305,10 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="17">
+      <c r="A43" s="16">
         <v>100340</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="17">
         <v>44226</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -10330,10 +10337,10 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="17">
+      <c r="A44" s="16">
         <v>100415</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="17">
         <v>44227</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -10362,10 +10369,10 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="17">
+      <c r="A45" s="16">
         <v>100421</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="17">
         <v>44227</v>
       </c>
       <c r="C45" s="8" t="s">
@@ -10394,10 +10401,10 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="17">
+      <c r="A46" s="16">
         <v>100304</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="17">
         <v>44228</v>
       </c>
       <c r="C46" s="8" t="s">
@@ -10426,10 +10433,10 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="17">
+      <c r="A47" s="16">
         <v>100414</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="17">
         <v>44229</v>
       </c>
       <c r="C47" s="8" t="s">
@@ -10458,10 +10465,10 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="17">
+      <c r="A48" s="16">
         <v>100420</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="17">
         <v>44229</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -10490,10 +10497,10 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="17">
+      <c r="A49" s="16">
         <v>100481</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="17">
         <v>44229</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -10522,10 +10529,10 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="17">
+      <c r="A50" s="16">
         <v>100352</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="17">
         <v>44230</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -10554,10 +10561,10 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="17">
+      <c r="A51" s="16">
         <v>100496</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="17">
         <v>44231</v>
       </c>
       <c r="C51" s="8" t="s">
@@ -10586,10 +10593,10 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="17">
+      <c r="A52" s="16">
         <v>100309</v>
       </c>
-      <c r="B52" s="18">
+      <c r="B52" s="17">
         <v>44232</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -10618,10 +10625,10 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="17">
+      <c r="A53" s="16">
         <v>100413</v>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="17">
         <v>44232</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -10650,10 +10657,10 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="17">
+      <c r="A54" s="16">
         <v>100498</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="17">
         <v>44233</v>
       </c>
       <c r="C54" s="8" t="s">
@@ -10682,10 +10689,10 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="17">
+      <c r="A55" s="16">
         <v>100499</v>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="17">
         <v>44234</v>
       </c>
       <c r="C55" s="8" t="s">
@@ -10714,10 +10721,10 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="17">
+      <c r="A56" s="16">
         <v>100509</v>
       </c>
-      <c r="B56" s="18">
+      <c r="B56" s="17">
         <v>44234</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -10746,10 +10753,10 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="17">
+      <c r="A57" s="16">
         <v>100371</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="17">
         <v>44235</v>
       </c>
       <c r="C57" s="8" t="s">
@@ -10778,10 +10785,10 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="17">
+      <c r="A58" s="16">
         <v>100412</v>
       </c>
-      <c r="B58" s="18">
+      <c r="B58" s="17">
         <v>44235</v>
       </c>
       <c r="C58" s="8" t="s">
@@ -10810,10 +10817,10 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="17">
+      <c r="A59" s="16">
         <v>100370</v>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="17">
         <v>44236</v>
       </c>
       <c r="C59" s="8" t="s">
@@ -10842,10 +10849,10 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="17">
+      <c r="A60" s="16">
         <v>100377</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="17">
         <v>44236</v>
       </c>
       <c r="C60" s="8" t="s">
@@ -10874,10 +10881,10 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="17">
+      <c r="A61" s="16">
         <v>100452</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="17">
         <v>44236</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -10906,10 +10913,10 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="17">
+      <c r="A62" s="16">
         <v>100459</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="17">
         <v>44236</v>
       </c>
       <c r="C62" s="8" t="s">
@@ -10938,10 +10945,10 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="17">
+      <c r="A63" s="16">
         <v>100325</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="17">
         <v>44240</v>
       </c>
       <c r="C63" s="8" t="s">
@@ -10970,10 +10977,10 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="17">
+      <c r="A64" s="16">
         <v>100419</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="17">
         <v>44240</v>
       </c>
       <c r="C64" s="8" t="s">
@@ -11002,10 +11009,10 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="17">
+      <c r="A65" s="16">
         <v>100512</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="17">
         <v>44240</v>
       </c>
       <c r="C65" s="8" t="s">
@@ -11034,10 +11041,10 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="17">
+      <c r="A66" s="16">
         <v>100513</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="17">
         <v>44240</v>
       </c>
       <c r="C66" s="8" t="s">
@@ -11066,10 +11073,10 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="17">
+      <c r="A67" s="16">
         <v>100514</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="17">
         <v>44240</v>
       </c>
       <c r="C67" s="8" t="s">
@@ -11098,10 +11105,10 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="17">
+      <c r="A68" s="16">
         <v>100471</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="17">
         <v>44242</v>
       </c>
       <c r="C68" s="8" t="s">
@@ -11130,10 +11137,10 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="17">
+      <c r="A69" s="16">
         <v>100396</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="17">
         <v>44243</v>
       </c>
       <c r="C69" s="8" t="s">
@@ -11162,10 +11169,10 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="17">
+      <c r="A70" s="16">
         <v>100436</v>
       </c>
-      <c r="B70" s="18">
+      <c r="B70" s="17">
         <v>44244</v>
       </c>
       <c r="C70" s="8" t="s">
@@ -11194,10 +11201,10 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="17">
+      <c r="A71" s="16">
         <v>100492</v>
       </c>
-      <c r="B71" s="18">
+      <c r="B71" s="17">
         <v>44245</v>
       </c>
       <c r="C71" s="8" t="s">
@@ -11226,10 +11233,10 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="17">
+      <c r="A72" s="16">
         <v>100494</v>
       </c>
-      <c r="B72" s="18">
+      <c r="B72" s="17">
         <v>44245</v>
       </c>
       <c r="C72" s="8" t="s">
@@ -11258,10 +11265,10 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="17">
+      <c r="A73" s="16">
         <v>100493</v>
       </c>
-      <c r="B73" s="18">
+      <c r="B73" s="17">
         <v>44246</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -11290,10 +11297,10 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="17">
+      <c r="A74" s="16">
         <v>100351</v>
       </c>
-      <c r="B74" s="18">
+      <c r="B74" s="17">
         <v>44247</v>
       </c>
       <c r="C74" s="8" t="s">
@@ -11322,10 +11329,10 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="17">
+      <c r="A75" s="16">
         <v>100411</v>
       </c>
-      <c r="B75" s="18">
+      <c r="B75" s="17">
         <v>44247</v>
       </c>
       <c r="C75" s="8" t="s">
@@ -11354,10 +11361,10 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="17">
+      <c r="A76" s="16">
         <v>100469</v>
       </c>
-      <c r="B76" s="18">
+      <c r="B76" s="17">
         <v>44248</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -11386,10 +11393,10 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="17">
+      <c r="A77" s="16">
         <v>100418</v>
       </c>
-      <c r="B77" s="18">
+      <c r="B77" s="17">
         <v>44249</v>
       </c>
       <c r="C77" s="8" t="s">
@@ -11418,10 +11425,10 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="17">
+      <c r="A78" s="16">
         <v>100511</v>
       </c>
-      <c r="B78" s="18">
+      <c r="B78" s="17">
         <v>44249</v>
       </c>
       <c r="C78" s="8" t="s">
@@ -11450,10 +11457,10 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="17">
+      <c r="A79" s="16">
         <v>100536</v>
       </c>
-      <c r="B79" s="18">
+      <c r="B79" s="17">
         <v>44249</v>
       </c>
       <c r="C79" s="8" t="s">
@@ -11482,10 +11489,10 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="17">
+      <c r="A80" s="16">
         <v>100537</v>
       </c>
-      <c r="B80" s="18">
+      <c r="B80" s="17">
         <v>44249</v>
       </c>
       <c r="C80" s="8" t="s">
@@ -11514,10 +11521,10 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="17">
+      <c r="A81" s="16">
         <v>100394</v>
       </c>
-      <c r="B81" s="18">
+      <c r="B81" s="17">
         <v>44250</v>
       </c>
       <c r="C81" s="8" t="s">
@@ -11546,10 +11553,10 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="17">
+      <c r="A82" s="16">
         <v>100367</v>
       </c>
-      <c r="B82" s="18">
+      <c r="B82" s="17">
         <v>44251</v>
       </c>
       <c r="C82" s="8" t="s">
@@ -11578,10 +11585,10 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="17">
+      <c r="A83" s="16">
         <v>100408</v>
       </c>
-      <c r="B83" s="18">
+      <c r="B83" s="17">
         <v>44251</v>
       </c>
       <c r="C83" s="8" t="s">
@@ -11610,10 +11617,10 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="17">
+      <c r="A84" s="16">
         <v>100410</v>
       </c>
-      <c r="B84" s="18">
+      <c r="B84" s="17">
         <v>44251</v>
       </c>
       <c r="C84" s="8" t="s">
@@ -11642,10 +11649,10 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="17">
+      <c r="A85" s="16">
         <v>100369</v>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="17">
         <v>44252</v>
       </c>
       <c r="C85" s="8" t="s">
@@ -11674,10 +11681,10 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="17">
+      <c r="A86" s="16">
         <v>100409</v>
       </c>
-      <c r="B86" s="18">
+      <c r="B86" s="17">
         <v>44252</v>
       </c>
       <c r="C86" s="8" t="s">
@@ -11706,10 +11713,10 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="17">
+      <c r="A87" s="16">
         <v>100546</v>
       </c>
-      <c r="B87" s="18">
+      <c r="B87" s="17">
         <v>44254</v>
       </c>
       <c r="C87" s="8" t="s">
@@ -11738,10 +11745,10 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="17">
+      <c r="A88" s="16">
         <v>100434</v>
       </c>
-      <c r="B88" s="18">
+      <c r="B88" s="17">
         <v>44256</v>
       </c>
       <c r="C88" s="8" t="s">
@@ -11770,10 +11777,10 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="17">
+      <c r="A89" s="16">
         <v>100523</v>
       </c>
-      <c r="B89" s="18">
+      <c r="B89" s="17">
         <v>44256</v>
       </c>
       <c r="C89" s="8" t="s">
@@ -11802,10 +11809,10 @@
       </c>
     </row>
     <row r="90" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="17">
+      <c r="A90" s="16">
         <v>100433</v>
       </c>
-      <c r="B90" s="18">
+      <c r="B90" s="17">
         <v>44257</v>
       </c>
       <c r="C90" s="8" t="s">
@@ -11834,10 +11841,10 @@
       </c>
     </row>
     <row r="91" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="17">
+      <c r="A91" s="16">
         <v>100566</v>
       </c>
-      <c r="B91" s="18">
+      <c r="B91" s="17">
         <v>44257</v>
       </c>
       <c r="C91" s="8" t="s">
@@ -11866,10 +11873,10 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="17">
+      <c r="A92" s="16">
         <v>100522</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="17">
         <v>44260</v>
       </c>
       <c r="C92" s="8" t="s">
@@ -11898,10 +11905,10 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="17">
+      <c r="A93" s="16">
         <v>100457</v>
       </c>
-      <c r="B93" s="18">
+      <c r="B93" s="17">
         <v>44261</v>
       </c>
       <c r="C93" s="8" t="s">
@@ -11930,10 +11937,10 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="17">
+      <c r="A94" s="16">
         <v>100521</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="17">
         <v>44261</v>
       </c>
       <c r="C94" s="8" t="s">
@@ -11962,10 +11969,10 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="17">
+      <c r="A95" s="16">
         <v>100532</v>
       </c>
-      <c r="B95" s="18">
+      <c r="B95" s="17">
         <v>44262</v>
       </c>
       <c r="C95" s="8" t="s">
@@ -11994,10 +12001,10 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="17">
+      <c r="A96" s="16">
         <v>100533</v>
       </c>
-      <c r="B96" s="18">
+      <c r="B96" s="17">
         <v>44262</v>
       </c>
       <c r="C96" s="8" t="s">
@@ -12026,10 +12033,10 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="17">
+      <c r="A97" s="16">
         <v>100467</v>
       </c>
-      <c r="B97" s="18">
+      <c r="B97" s="17">
         <v>44263</v>
       </c>
       <c r="C97" s="8" t="s">
@@ -12058,10 +12065,10 @@
       </c>
     </row>
     <row r="98" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="17">
+      <c r="A98" s="16">
         <v>100583</v>
       </c>
-      <c r="B98" s="18">
+      <c r="B98" s="17">
         <v>44263</v>
       </c>
       <c r="C98" s="8" t="s">
@@ -12090,10 +12097,10 @@
       </c>
     </row>
     <row r="99" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="17">
+      <c r="A99" s="16">
         <v>100404</v>
       </c>
-      <c r="B99" s="18">
+      <c r="B99" s="17">
         <v>44264</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -12122,10 +12129,10 @@
       </c>
     </row>
     <row r="100" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="17">
+      <c r="A100" s="16">
         <v>100554</v>
       </c>
-      <c r="B100" s="18">
+      <c r="B100" s="17">
         <v>44264</v>
       </c>
       <c r="C100" s="8" t="s">
@@ -12154,10 +12161,10 @@
       </c>
     </row>
     <row r="101" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="17">
+      <c r="A101" s="16">
         <v>100446</v>
       </c>
-      <c r="B101" s="18">
+      <c r="B101" s="17">
         <v>44266</v>
       </c>
       <c r="C101" s="8" t="s">
@@ -12186,10 +12193,10 @@
       </c>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="17">
+      <c r="A102" s="16">
         <v>100465</v>
       </c>
-      <c r="B102" s="18">
+      <c r="B102" s="17">
         <v>44267</v>
       </c>
       <c r="C102" s="8" t="s">
@@ -12218,10 +12225,10 @@
       </c>
     </row>
     <row r="103" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="17">
+      <c r="A103" s="16">
         <v>100490</v>
       </c>
-      <c r="B103" s="18">
+      <c r="B103" s="17">
         <v>44267</v>
       </c>
       <c r="C103" s="8" t="s">
@@ -12250,10 +12257,10 @@
       </c>
     </row>
     <row r="104" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="17">
+      <c r="A104" s="16">
         <v>100456</v>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" s="17">
         <v>44269</v>
       </c>
       <c r="C104" s="8" t="s">
@@ -12282,10 +12289,10 @@
       </c>
     </row>
     <row r="105" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="17">
+      <c r="A105" s="16">
         <v>100489</v>
       </c>
-      <c r="B105" s="18">
+      <c r="B105" s="17">
         <v>44269</v>
       </c>
       <c r="C105" s="8" t="s">
@@ -12314,10 +12321,10 @@
       </c>
     </row>
     <row r="106" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="17">
+      <c r="A106" s="16">
         <v>100545</v>
       </c>
-      <c r="B106" s="18">
+      <c r="B106" s="17">
         <v>44269</v>
       </c>
       <c r="C106" s="8" t="s">
@@ -12346,10 +12353,10 @@
       </c>
     </row>
     <row r="107" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="17">
+      <c r="A107" s="16">
         <v>100543</v>
       </c>
-      <c r="B107" s="18">
+      <c r="B107" s="17">
         <v>44270</v>
       </c>
       <c r="C107" s="8" t="s">
@@ -12378,10 +12385,10 @@
       </c>
     </row>
     <row r="108" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="17">
+      <c r="A108" s="16">
         <v>100564</v>
       </c>
-      <c r="B108" s="18">
+      <c r="B108" s="17">
         <v>44270</v>
       </c>
       <c r="C108" s="8" t="s">
@@ -12410,10 +12417,10 @@
       </c>
     </row>
     <row r="109" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="17">
+      <c r="A109" s="16">
         <v>100430</v>
       </c>
-      <c r="B109" s="18">
+      <c r="B109" s="17">
         <v>44272</v>
       </c>
       <c r="C109" s="8" t="s">
@@ -12442,10 +12449,10 @@
       </c>
     </row>
     <row r="110" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A110" s="17">
+      <c r="A110" s="16">
         <v>100477</v>
       </c>
-      <c r="B110" s="18">
+      <c r="B110" s="17">
         <v>44272</v>
       </c>
       <c r="C110" s="8" t="s">
@@ -12474,10 +12481,10 @@
       </c>
     </row>
     <row r="111" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="17">
+      <c r="A111" s="16">
         <v>100478</v>
       </c>
-      <c r="B111" s="18">
+      <c r="B111" s="17">
         <v>44272</v>
       </c>
       <c r="C111" s="8" t="s">
@@ -12506,10 +12513,10 @@
       </c>
     </row>
     <row r="112" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="17">
+      <c r="A112" s="16">
         <v>100444</v>
       </c>
-      <c r="B112" s="18">
+      <c r="B112" s="17">
         <v>44276</v>
       </c>
       <c r="C112" s="8" t="s">
@@ -12538,10 +12545,10 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="17">
+      <c r="A113" s="16">
         <v>100582</v>
       </c>
-      <c r="B113" s="18">
+      <c r="B113" s="17">
         <v>44277</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -12570,10 +12577,10 @@
       </c>
     </row>
     <row r="114" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="17">
+      <c r="A114" s="16">
         <v>100487</v>
       </c>
-      <c r="B114" s="18">
+      <c r="B114" s="17">
         <v>44278</v>
       </c>
       <c r="C114" s="8" t="s">
@@ -12602,10 +12609,10 @@
       </c>
     </row>
     <row r="115" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="17">
+      <c r="A115" s="16">
         <v>100519</v>
       </c>
-      <c r="B115" s="18">
+      <c r="B115" s="17">
         <v>44280</v>
       </c>
       <c r="C115" s="8" t="s">
@@ -12634,10 +12641,10 @@
       </c>
     </row>
     <row r="116" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A116" s="17">
+      <c r="A116" s="16">
         <v>100462</v>
       </c>
-      <c r="B116" s="18">
+      <c r="B116" s="17">
         <v>44281</v>
       </c>
       <c r="C116" s="8" t="s">
@@ -12666,10 +12673,10 @@
       </c>
     </row>
     <row r="117" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="17">
+      <c r="A117" s="16">
         <v>100486</v>
       </c>
-      <c r="B117" s="18">
+      <c r="B117" s="17">
         <v>44281</v>
       </c>
       <c r="C117" s="8" t="s">
@@ -12698,10 +12705,10 @@
       </c>
     </row>
     <row r="118" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A118" s="17">
+      <c r="A118" s="16">
         <v>100463</v>
       </c>
-      <c r="B118" s="18">
+      <c r="B118" s="17">
         <v>44282</v>
       </c>
       <c r="C118" s="8" t="s">
@@ -12730,10 +12737,10 @@
       </c>
     </row>
     <row r="119" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A119" s="17">
+      <c r="A119" s="16">
         <v>100595</v>
       </c>
-      <c r="B119" s="18">
+      <c r="B119" s="17">
         <v>44282</v>
       </c>
       <c r="C119" s="8" t="s">
@@ -12762,10 +12769,10 @@
       </c>
     </row>
     <row r="120" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="17">
+      <c r="A120" s="16">
         <v>100617</v>
       </c>
-      <c r="B120" s="18">
+      <c r="B120" s="17">
         <v>44282</v>
       </c>
       <c r="C120" s="8" t="s">
@@ -12794,10 +12801,10 @@
       </c>
     </row>
     <row r="121" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="17">
+      <c r="A121" s="16">
         <v>100580</v>
       </c>
-      <c r="B121" s="18">
+      <c r="B121" s="17">
         <v>44285</v>
       </c>
       <c r="C121" s="8" t="s">
@@ -12826,10 +12833,10 @@
       </c>
     </row>
     <row r="122" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="17">
+      <c r="A122" s="16">
         <v>100581</v>
       </c>
-      <c r="B122" s="18">
+      <c r="B122" s="17">
         <v>44285</v>
       </c>
       <c r="C122" s="8" t="s">
@@ -12858,10 +12865,10 @@
       </c>
     </row>
     <row r="123" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="17">
+      <c r="A123" s="16">
         <v>100475</v>
       </c>
-      <c r="B123" s="18">
+      <c r="B123" s="17">
         <v>44286</v>
       </c>
       <c r="C123" s="8" t="s">
@@ -12890,10 +12897,10 @@
       </c>
     </row>
     <row r="124" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="17">
+      <c r="A124" s="16">
         <v>100503</v>
       </c>
-      <c r="B124" s="18">
+      <c r="B124" s="17">
         <v>44286</v>
       </c>
       <c r="C124" s="8" t="s">
@@ -12922,10 +12929,10 @@
       </c>
     </row>
     <row r="125" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A125" s="17">
+      <c r="A125" s="16">
         <v>100504</v>
       </c>
-      <c r="B125" s="18">
+      <c r="B125" s="17">
         <v>44286</v>
       </c>
       <c r="C125" s="8" t="s">
@@ -12954,10 +12961,10 @@
       </c>
     </row>
     <row r="126" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="17">
+      <c r="A126" s="16">
         <v>100616</v>
       </c>
-      <c r="B126" s="18">
+      <c r="B126" s="17">
         <v>44286</v>
       </c>
       <c r="C126" s="8" t="s">
@@ -12986,10 +12993,10 @@
       </c>
     </row>
     <row r="127" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A127" s="17">
+      <c r="A127" s="16">
         <v>100614</v>
       </c>
-      <c r="B127" s="18">
+      <c r="B127" s="17">
         <v>44289</v>
       </c>
       <c r="C127" s="8" t="s">
@@ -13018,10 +13025,10 @@
       </c>
     </row>
     <row r="128" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="17">
+      <c r="A128" s="16">
         <v>100529</v>
       </c>
-      <c r="B128" s="18">
+      <c r="B128" s="17">
         <v>44291</v>
       </c>
       <c r="C128" s="8" t="s">
@@ -13050,10 +13057,10 @@
       </c>
     </row>
     <row r="129" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A129" s="17">
+      <c r="A129" s="16">
         <v>100551</v>
       </c>
-      <c r="B129" s="18">
+      <c r="B129" s="17">
         <v>44292</v>
       </c>
       <c r="C129" s="8" t="s">
@@ -13082,10 +13089,10 @@
       </c>
     </row>
     <row r="130" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="17">
+      <c r="A130" s="16">
         <v>100501</v>
       </c>
-      <c r="B130" s="18">
+      <c r="B130" s="17">
         <v>44293</v>
       </c>
       <c r="C130" s="8" t="s">
@@ -13114,10 +13121,10 @@
       </c>
     </row>
     <row r="131" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A131" s="17">
+      <c r="A131" s="16">
         <v>100516</v>
       </c>
-      <c r="B131" s="18">
+      <c r="B131" s="17">
         <v>44293</v>
       </c>
       <c r="C131" s="8" t="s">
@@ -13146,10 +13153,10 @@
       </c>
     </row>
     <row r="132" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="17">
+      <c r="A132" s="16">
         <v>100542</v>
       </c>
-      <c r="B132" s="18">
+      <c r="B132" s="17">
         <v>44293</v>
       </c>
       <c r="C132" s="8" t="s">
@@ -13178,10 +13185,10 @@
       </c>
     </row>
     <row r="133" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="17">
+      <c r="A133" s="16">
         <v>100625</v>
       </c>
-      <c r="B133" s="18">
+      <c r="B133" s="17">
         <v>44293</v>
       </c>
       <c r="C133" s="8" t="s">
@@ -13210,10 +13217,10 @@
       </c>
     </row>
     <row r="134" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="17">
+      <c r="A134" s="16">
         <v>100540</v>
       </c>
-      <c r="B134" s="18">
+      <c r="B134" s="17">
         <v>44295</v>
       </c>
       <c r="C134" s="8" t="s">
@@ -13242,10 +13249,10 @@
       </c>
     </row>
     <row r="135" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A135" s="17">
+      <c r="A135" s="16">
         <v>100663</v>
       </c>
-      <c r="B135" s="18">
+      <c r="B135" s="17">
         <v>44296</v>
       </c>
       <c r="C135" s="8" t="s">
@@ -13274,10 +13281,10 @@
       </c>
     </row>
     <row r="136" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A136" s="17">
+      <c r="A136" s="16">
         <v>100539</v>
       </c>
-      <c r="B136" s="18">
+      <c r="B136" s="17">
         <v>44297</v>
       </c>
       <c r="C136" s="8" t="s">
@@ -13306,10 +13313,10 @@
       </c>
     </row>
     <row r="137" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A137" s="17">
+      <c r="A137" s="16">
         <v>100642</v>
       </c>
-      <c r="B137" s="18">
+      <c r="B137" s="17">
         <v>44297</v>
       </c>
       <c r="C137" s="8" t="s">
@@ -13338,10 +13345,10 @@
       </c>
     </row>
     <row r="138" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="17">
+      <c r="A138" s="16">
         <v>100549</v>
       </c>
-      <c r="B138" s="18">
+      <c r="B138" s="17">
         <v>44301</v>
       </c>
       <c r="C138" s="8" t="s">
@@ -13370,10 +13377,10 @@
       </c>
     </row>
     <row r="139" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A139" s="17">
+      <c r="A139" s="16">
         <v>100680</v>
       </c>
-      <c r="B139" s="18">
+      <c r="B139" s="17">
         <v>44301</v>
       </c>
       <c r="C139" s="8" t="s">
@@ -13402,10 +13409,10 @@
       </c>
     </row>
     <row r="140" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A140" s="17">
+      <c r="A140" s="16">
         <v>100560</v>
       </c>
-      <c r="B140" s="18">
+      <c r="B140" s="17">
         <v>44302</v>
       </c>
       <c r="C140" s="8" t="s">
@@ -13434,10 +13441,10 @@
       </c>
     </row>
     <row r="141" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="17">
+      <c r="A141" s="16">
         <v>100629</v>
       </c>
-      <c r="B141" s="18">
+      <c r="B141" s="17">
         <v>44302</v>
       </c>
       <c r="C141" s="8" t="s">
@@ -13466,10 +13473,10 @@
       </c>
     </row>
     <row r="142" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="17">
+      <c r="A142" s="16">
         <v>100631</v>
       </c>
-      <c r="B142" s="18">
+      <c r="B142" s="17">
         <v>44302</v>
       </c>
       <c r="C142" s="8" t="s">
@@ -13498,10 +13505,10 @@
       </c>
     </row>
     <row r="143" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="17">
+      <c r="A143" s="16">
         <v>100572</v>
       </c>
-      <c r="B143" s="18">
+      <c r="B143" s="17">
         <v>44303</v>
       </c>
       <c r="C143" s="8" t="s">
@@ -13530,10 +13537,10 @@
       </c>
     </row>
     <row r="144" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="17">
+      <c r="A144" s="16">
         <v>100630</v>
       </c>
-      <c r="B144" s="18">
+      <c r="B144" s="17">
         <v>44303</v>
       </c>
       <c r="C144" s="8" t="s">
@@ -13562,10 +13569,10 @@
       </c>
     </row>
     <row r="145" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="17">
+      <c r="A145" s="16">
         <v>100637</v>
       </c>
-      <c r="B145" s="18">
+      <c r="B145" s="17">
         <v>44303</v>
       </c>
       <c r="C145" s="8" t="s">
@@ -13594,10 +13601,10 @@
       </c>
     </row>
     <row r="146" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="17">
+      <c r="A146" s="16">
         <v>100659</v>
       </c>
-      <c r="B146" s="18">
+      <c r="B146" s="17">
         <v>44303</v>
       </c>
       <c r="C146" s="8" t="s">
@@ -13626,10 +13633,10 @@
       </c>
     </row>
     <row r="147" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A147" s="17">
+      <c r="A147" s="16">
         <v>100527</v>
       </c>
-      <c r="B147" s="18">
+      <c r="B147" s="17">
         <v>44304</v>
       </c>
       <c r="C147" s="8" t="s">
@@ -13658,10 +13665,10 @@
       </c>
     </row>
     <row r="148" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A148" s="17">
+      <c r="A148" s="16">
         <v>100638</v>
       </c>
-      <c r="B148" s="18">
+      <c r="B148" s="17">
         <v>44304</v>
       </c>
       <c r="C148" s="8" t="s">
@@ -13690,10 +13697,10 @@
       </c>
     </row>
     <row r="149" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="17">
+      <c r="A149" s="16">
         <v>100679</v>
       </c>
-      <c r="B149" s="18">
+      <c r="B149" s="17">
         <v>44304</v>
       </c>
       <c r="C149" s="8" t="s">
@@ -13722,10 +13729,10 @@
       </c>
     </row>
     <row r="150" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="17">
+      <c r="A150" s="16">
         <v>100678</v>
       </c>
-      <c r="B150" s="18">
+      <c r="B150" s="17">
         <v>44307</v>
       </c>
       <c r="C150" s="8" t="s">
@@ -13754,10 +13761,10 @@
       </c>
     </row>
     <row r="151" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="17">
+      <c r="A151" s="16">
         <v>100570</v>
       </c>
-      <c r="B151" s="18">
+      <c r="B151" s="17">
         <v>44308</v>
       </c>
       <c r="C151" s="8" t="s">
@@ -13786,10 +13793,10 @@
       </c>
     </row>
     <row r="152" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="17">
+      <c r="A152" s="16">
         <v>100578</v>
       </c>
-      <c r="B152" s="18">
+      <c r="B152" s="17">
         <v>44311</v>
       </c>
       <c r="C152" s="8" t="s">
@@ -13818,10 +13825,10 @@
       </c>
     </row>
     <row r="153" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A153" s="17">
+      <c r="A153" s="16">
         <v>100611</v>
       </c>
-      <c r="B153" s="18">
+      <c r="B153" s="17">
         <v>44311</v>
       </c>
       <c r="C153" s="8" t="s">
@@ -13850,10 +13857,10 @@
       </c>
     </row>
     <row r="154" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A154" s="17">
+      <c r="A154" s="16">
         <v>100621</v>
       </c>
-      <c r="B154" s="18">
+      <c r="B154" s="17">
         <v>44311</v>
       </c>
       <c r="C154" s="8" t="s">
@@ -13882,10 +13889,10 @@
       </c>
     </row>
     <row r="155" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A155" s="17">
+      <c r="A155" s="16">
         <v>100622</v>
       </c>
-      <c r="B155" s="18">
+      <c r="B155" s="17">
         <v>44311</v>
       </c>
       <c r="C155" s="8" t="s">
@@ -13914,10 +13921,10 @@
       </c>
     </row>
     <row r="156" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A156" s="17">
+      <c r="A156" s="16">
         <v>100623</v>
       </c>
-      <c r="B156" s="18">
+      <c r="B156" s="17">
         <v>44311</v>
       </c>
       <c r="C156" s="8" t="s">
@@ -13946,10 +13953,10 @@
       </c>
     </row>
     <row r="157" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A157" s="17">
+      <c r="A157" s="16">
         <v>100604</v>
       </c>
-      <c r="B157" s="18">
+      <c r="B157" s="17">
         <v>44312</v>
       </c>
       <c r="C157" s="8" t="s">
@@ -13978,10 +13985,10 @@
       </c>
     </row>
     <row r="158" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A158" s="17">
+      <c r="A158" s="16">
         <v>100610</v>
       </c>
-      <c r="B158" s="18">
+      <c r="B158" s="17">
         <v>44313</v>
       </c>
       <c r="C158" s="8" t="s">
@@ -14010,10 +14017,10 @@
       </c>
     </row>
     <row r="159" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A159" s="17">
+      <c r="A159" s="16">
         <v>100591</v>
       </c>
-      <c r="B159" s="18">
+      <c r="B159" s="17">
         <v>44315</v>
       </c>
       <c r="C159" s="8" t="s">
@@ -14042,10 +14049,10 @@
       </c>
     </row>
     <row r="160" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A160" s="17">
+      <c r="A160" s="16">
         <v>100557</v>
       </c>
-      <c r="B160" s="18">
+      <c r="B160" s="17">
         <v>44316</v>
       </c>
       <c r="C160" s="8" t="s">
@@ -14074,10 +14081,10 @@
       </c>
     </row>
     <row r="161" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A161" s="17">
+      <c r="A161" s="16">
         <v>100636</v>
       </c>
-      <c r="B161" s="18">
+      <c r="B161" s="17">
         <v>44316</v>
       </c>
       <c r="C161" s="8" t="s">
@@ -14106,10 +14113,10 @@
       </c>
     </row>
     <row r="162" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A162" s="17">
+      <c r="A162" s="16">
         <v>100628</v>
       </c>
-      <c r="B162" s="18">
+      <c r="B162" s="17">
         <v>44317</v>
       </c>
       <c r="C162" s="8" t="s">
@@ -14138,10 +14145,10 @@
       </c>
     </row>
     <row r="163" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A163" s="17">
+      <c r="A163" s="16">
         <v>100650</v>
       </c>
-      <c r="B163" s="18">
+      <c r="B163" s="17">
         <v>44318</v>
       </c>
       <c r="C163" s="8" t="s">
@@ -14170,10 +14177,10 @@
       </c>
     </row>
     <row r="164" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A164" s="17">
+      <c r="A164" s="16">
         <v>100651</v>
       </c>
-      <c r="B164" s="18">
+      <c r="B164" s="17">
         <v>44318</v>
       </c>
       <c r="C164" s="8" t="s">
@@ -14202,10 +14209,10 @@
       </c>
     </row>
     <row r="165" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A165" s="17">
+      <c r="A165" s="16">
         <v>100569</v>
       </c>
-      <c r="B165" s="18">
+      <c r="B165" s="17">
         <v>44319</v>
       </c>
       <c r="C165" s="8" t="s">
@@ -14234,10 +14241,10 @@
       </c>
     </row>
     <row r="166" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A166" s="17">
+      <c r="A166" s="16">
         <v>100609</v>
       </c>
-      <c r="B166" s="18">
+      <c r="B166" s="17">
         <v>44319</v>
       </c>
       <c r="C166" s="8" t="s">
@@ -14266,10 +14273,10 @@
       </c>
     </row>
     <row r="167" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A167" s="17">
+      <c r="A167" s="16">
         <v>100649</v>
       </c>
-      <c r="B167" s="18">
+      <c r="B167" s="17">
         <v>44320</v>
       </c>
       <c r="C167" s="8" t="s">
@@ -14298,10 +14305,10 @@
       </c>
     </row>
     <row r="168" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A168" s="17">
+      <c r="A168" s="16">
         <v>100656</v>
       </c>
-      <c r="B168" s="18">
+      <c r="B168" s="17">
         <v>44322</v>
       </c>
       <c r="C168" s="8" t="s">
@@ -14330,10 +14337,10 @@
       </c>
     </row>
     <row r="169" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A169" s="17">
+      <c r="A169" s="16">
         <v>100677</v>
       </c>
-      <c r="B169" s="18">
+      <c r="B169" s="17">
         <v>44322</v>
       </c>
       <c r="C169" s="8" t="s">
@@ -14362,10 +14369,10 @@
       </c>
     </row>
     <row r="170" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A170" s="17">
+      <c r="A170" s="16">
         <v>100704</v>
       </c>
-      <c r="B170" s="18">
+      <c r="B170" s="17">
         <v>44322</v>
       </c>
       <c r="C170" s="8" t="s">
@@ -14394,10 +14401,10 @@
       </c>
     </row>
     <row r="171" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A171" s="17">
+      <c r="A171" s="16">
         <v>100713</v>
       </c>
-      <c r="B171" s="18">
+      <c r="B171" s="17">
         <v>44322</v>
       </c>
       <c r="C171" s="8" t="s">
@@ -14426,10 +14433,10 @@
       </c>
     </row>
     <row r="172" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A172" s="17">
+      <c r="A172" s="16">
         <v>100584</v>
       </c>
-      <c r="B172" s="18">
+      <c r="B172" s="17">
         <v>44323</v>
       </c>
       <c r="C172" s="8" t="s">
@@ -14458,10 +14465,10 @@
       </c>
     </row>
     <row r="173" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A173" s="17">
+      <c r="A173" s="16">
         <v>100674</v>
       </c>
-      <c r="B173" s="18">
+      <c r="B173" s="17">
         <v>44323</v>
       </c>
       <c r="C173" s="8" t="s">
@@ -14490,10 +14497,10 @@
       </c>
     </row>
     <row r="174" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A174" s="17">
+      <c r="A174" s="16">
         <v>100589</v>
       </c>
-      <c r="B174" s="18">
+      <c r="B174" s="17">
         <v>44324</v>
       </c>
       <c r="C174" s="8" t="s">
@@ -14522,10 +14529,10 @@
       </c>
     </row>
     <row r="175" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A175" s="17">
+      <c r="A175" s="16">
         <v>100590</v>
       </c>
-      <c r="B175" s="18">
+      <c r="B175" s="17">
         <v>44324</v>
       </c>
       <c r="C175" s="8" t="s">
@@ -14554,10 +14561,10 @@
       </c>
     </row>
     <row r="176" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A176" s="17">
+      <c r="A176" s="16">
         <v>100675</v>
       </c>
-      <c r="B176" s="18">
+      <c r="B176" s="17">
         <v>44324</v>
       </c>
       <c r="C176" s="8" t="s">
@@ -14586,10 +14593,10 @@
       </c>
     </row>
     <row r="177" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A177" s="17">
+      <c r="A177" s="16">
         <v>100648</v>
       </c>
-      <c r="B177" s="18">
+      <c r="B177" s="17">
         <v>44325</v>
       </c>
       <c r="C177" s="8" t="s">
@@ -14618,10 +14625,10 @@
       </c>
     </row>
     <row r="178" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A178" s="17">
+      <c r="A178" s="16">
         <v>100683</v>
       </c>
-      <c r="B178" s="18">
+      <c r="B178" s="17">
         <v>44325</v>
       </c>
       <c r="C178" s="8" t="s">
@@ -14650,10 +14657,10 @@
       </c>
     </row>
     <row r="179" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A179" s="17">
+      <c r="A179" s="16">
         <v>100647</v>
       </c>
-      <c r="B179" s="18">
+      <c r="B179" s="17">
         <v>44326</v>
       </c>
       <c r="C179" s="8" t="s">
@@ -14682,10 +14689,10 @@
       </c>
     </row>
     <row r="180" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A180" s="17">
+      <c r="A180" s="16">
         <v>100602</v>
       </c>
-      <c r="B180" s="18">
+      <c r="B180" s="17">
         <v>44327</v>
       </c>
       <c r="C180" s="8" t="s">
@@ -14714,10 +14721,10 @@
       </c>
     </row>
     <row r="181" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A181" s="17">
+      <c r="A181" s="16">
         <v>100672</v>
       </c>
-      <c r="B181" s="18">
+      <c r="B181" s="17">
         <v>44327</v>
       </c>
       <c r="C181" s="8" t="s">
@@ -14746,10 +14753,10 @@
       </c>
     </row>
     <row r="182" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="17">
+      <c r="A182" s="16">
         <v>100600</v>
       </c>
-      <c r="B182" s="18">
+      <c r="B182" s="17">
         <v>44328</v>
       </c>
       <c r="C182" s="8" t="s">
@@ -14778,10 +14785,10 @@
       </c>
     </row>
     <row r="183" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="17">
+      <c r="A183" s="16">
         <v>100655</v>
       </c>
-      <c r="B183" s="18">
+      <c r="B183" s="17">
         <v>44328</v>
       </c>
       <c r="C183" s="8" t="s">
@@ -14810,10 +14817,10 @@
       </c>
     </row>
     <row r="184" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A184" s="17">
+      <c r="A184" s="16">
         <v>100671</v>
       </c>
-      <c r="B184" s="18">
+      <c r="B184" s="17">
         <v>44328</v>
       </c>
       <c r="C184" s="8" t="s">
@@ -14842,10 +14849,10 @@
       </c>
     </row>
     <row r="185" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A185" s="17">
+      <c r="A185" s="16">
         <v>100646</v>
       </c>
-      <c r="B185" s="18">
+      <c r="B185" s="17">
         <v>44329</v>
       </c>
       <c r="C185" s="8" t="s">
@@ -14874,10 +14881,10 @@
       </c>
     </row>
     <row r="186" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A186" s="17">
+      <c r="A186" s="16">
         <v>100618</v>
       </c>
-      <c r="B186" s="18">
+      <c r="B186" s="17">
         <v>44330</v>
       </c>
       <c r="C186" s="8" t="s">
@@ -14906,10 +14913,10 @@
       </c>
     </row>
     <row r="187" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A187" s="17">
+      <c r="A187" s="16">
         <v>100681</v>
       </c>
-      <c r="B187" s="18">
+      <c r="B187" s="17">
         <v>44330</v>
       </c>
       <c r="C187" s="8" t="s">
@@ -14938,10 +14945,10 @@
       </c>
     </row>
     <row r="188" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A188" s="17">
+      <c r="A188" s="16">
         <v>100619</v>
       </c>
-      <c r="B188" s="18">
+      <c r="B188" s="17">
         <v>44331</v>
       </c>
       <c r="C188" s="8" t="s">
@@ -14970,10 +14977,10 @@
       </c>
     </row>
     <row r="189" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A189" s="17">
+      <c r="A189" s="16">
         <v>100627</v>
       </c>
-      <c r="B189" s="18">
+      <c r="B189" s="17">
         <v>44332</v>
       </c>
       <c r="C189" s="8" t="s">
@@ -15002,10 +15009,10 @@
       </c>
     </row>
     <row r="190" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A190" s="17">
+      <c r="A190" s="16">
         <v>100670</v>
       </c>
-      <c r="B190" s="18">
+      <c r="B190" s="17">
         <v>44332</v>
       </c>
       <c r="C190" s="8" t="s">
@@ -15034,10 +15041,10 @@
       </c>
     </row>
     <row r="191" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A191" s="17">
+      <c r="A191" s="16">
         <v>100689</v>
       </c>
-      <c r="B191" s="18">
+      <c r="B191" s="17">
         <v>44332</v>
       </c>
       <c r="C191" s="8" t="s">
@@ -15066,10 +15073,10 @@
       </c>
     </row>
     <row r="192" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A192" s="17">
+      <c r="A192" s="16">
         <v>100726</v>
       </c>
-      <c r="B192" s="18">
+      <c r="B192" s="17">
         <v>44332</v>
       </c>
       <c r="C192" s="8" t="s">
@@ -15098,10 +15105,10 @@
       </c>
     </row>
     <row r="193" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A193" s="17">
+      <c r="A193" s="16">
         <v>100702</v>
       </c>
-      <c r="B193" s="18">
+      <c r="B193" s="17">
         <v>44333</v>
       </c>
       <c r="C193" s="8" t="s">
@@ -15130,10 +15137,10 @@
       </c>
     </row>
     <row r="194" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A194" s="17">
+      <c r="A194" s="16">
         <v>100703</v>
       </c>
-      <c r="B194" s="18">
+      <c r="B194" s="17">
         <v>44333</v>
       </c>
       <c r="C194" s="8" t="s">
@@ -15162,10 +15169,10 @@
       </c>
     </row>
     <row r="195" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A195" s="17">
+      <c r="A195" s="16">
         <v>100635</v>
       </c>
-      <c r="B195" s="18">
+      <c r="B195" s="17">
         <v>44334</v>
       </c>
       <c r="C195" s="8" t="s">
@@ -15194,10 +15201,10 @@
       </c>
     </row>
     <row r="196" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A196" s="17">
+      <c r="A196" s="16">
         <v>100736</v>
       </c>
-      <c r="B196" s="18">
+      <c r="B196" s="17">
         <v>44334</v>
       </c>
       <c r="C196" s="8" t="s">
@@ -15226,10 +15233,10 @@
       </c>
     </row>
     <row r="197" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A197" s="17">
+      <c r="A197" s="16">
         <v>100737</v>
       </c>
-      <c r="B197" s="18">
+      <c r="B197" s="17">
         <v>44334</v>
       </c>
       <c r="C197" s="8" t="s">
@@ -15258,10 +15265,10 @@
       </c>
     </row>
     <row r="198" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A198" s="17">
+      <c r="A198" s="16">
         <v>100644</v>
       </c>
-      <c r="B198" s="18">
+      <c r="B198" s="17">
         <v>44335</v>
       </c>
       <c r="C198" s="8" t="s">
@@ -15290,10 +15297,10 @@
       </c>
     </row>
     <row r="199" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A199" s="17">
+      <c r="A199" s="16">
         <v>100643</v>
       </c>
-      <c r="B199" s="18">
+      <c r="B199" s="17">
         <v>44336</v>
       </c>
       <c r="C199" s="8" t="s">
@@ -15322,10 +15329,10 @@
       </c>
     </row>
     <row r="200" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A200" s="17">
+      <c r="A200" s="16">
         <v>100698</v>
       </c>
-      <c r="B200" s="18">
+      <c r="B200" s="17">
         <v>44336</v>
       </c>
       <c r="C200" s="8" t="s">
@@ -15354,10 +15361,10 @@
       </c>
     </row>
     <row r="201" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A201" s="17">
+      <c r="A201" s="16">
         <v>100652</v>
       </c>
-      <c r="B201" s="18">
+      <c r="B201" s="17">
         <v>44337</v>
       </c>
       <c r="C201" s="8" t="s">
@@ -15386,10 +15393,10 @@
       </c>
     </row>
     <row r="202" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A202" s="17">
+      <c r="A202" s="16">
         <v>100653</v>
       </c>
-      <c r="B202" s="18">
+      <c r="B202" s="17">
         <v>44337</v>
       </c>
       <c r="C202" s="8" t="s">
@@ -15418,10 +15425,10 @@
       </c>
     </row>
     <row r="203" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A203" s="17">
+      <c r="A203" s="16">
         <v>100705</v>
       </c>
-      <c r="B203" s="18">
+      <c r="B203" s="17">
         <v>44337</v>
       </c>
       <c r="C203" s="8" t="s">
@@ -15450,10 +15457,10 @@
       </c>
     </row>
     <row r="204" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A204" s="17">
+      <c r="A204" s="16">
         <v>100718</v>
       </c>
-      <c r="B204" s="18">
+      <c r="B204" s="17">
         <v>44337</v>
       </c>
       <c r="C204" s="8" t="s">
@@ -15482,10 +15489,10 @@
       </c>
     </row>
     <row r="205" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A205" s="17">
+      <c r="A205" s="16">
         <v>100744</v>
       </c>
-      <c r="B205" s="18">
+      <c r="B205" s="17">
         <v>44337</v>
       </c>
       <c r="C205" s="8" t="s">
@@ -15514,10 +15521,10 @@
       </c>
     </row>
     <row r="206" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A206" s="17">
+      <c r="A206" s="16">
         <v>100709</v>
       </c>
-      <c r="B206" s="18">
+      <c r="B206" s="17">
         <v>44338</v>
       </c>
       <c r="C206" s="8" t="s">
@@ -15546,10 +15553,10 @@
       </c>
     </row>
     <row r="207" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A207" s="17">
+      <c r="A207" s="16">
         <v>100749</v>
       </c>
-      <c r="B207" s="18">
+      <c r="B207" s="17">
         <v>44338</v>
       </c>
       <c r="C207" s="8" t="s">
@@ -15578,10 +15585,10 @@
       </c>
     </row>
     <row r="208" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A208" s="17">
+      <c r="A208" s="16">
         <v>100751</v>
       </c>
-      <c r="B208" s="18">
+      <c r="B208" s="17">
         <v>44338</v>
       </c>
       <c r="C208" s="8" t="s">
@@ -15610,10 +15617,10 @@
       </c>
     </row>
     <row r="209" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A209" s="17">
+      <c r="A209" s="16">
         <v>100752</v>
       </c>
-      <c r="B209" s="18">
+      <c r="B209" s="17">
         <v>44338</v>
       </c>
       <c r="C209" s="8" t="s">
@@ -15642,10 +15649,10 @@
       </c>
     </row>
     <row r="210" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A210" s="17">
+      <c r="A210" s="16">
         <v>100696</v>
       </c>
-      <c r="B210" s="18">
+      <c r="B210" s="17">
         <v>44339</v>
       </c>
       <c r="C210" s="8" t="s">
@@ -15674,10 +15681,10 @@
       </c>
     </row>
     <row r="211" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A211" s="17">
+      <c r="A211" s="16">
         <v>100742</v>
       </c>
-      <c r="B211" s="18">
+      <c r="B211" s="17">
         <v>44339</v>
       </c>
       <c r="C211" s="8" t="s">
@@ -15706,10 +15713,10 @@
       </c>
     </row>
     <row r="212" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A212" s="17">
+      <c r="A212" s="16">
         <v>100666</v>
       </c>
-      <c r="B212" s="18">
+      <c r="B212" s="17">
         <v>44340</v>
       </c>
       <c r="C212" s="8" t="s">
@@ -15738,10 +15745,10 @@
       </c>
     </row>
     <row r="213" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A213" s="17">
+      <c r="A213" s="16">
         <v>100667</v>
       </c>
-      <c r="B213" s="18">
+      <c r="B213" s="17">
         <v>44341</v>
       </c>
       <c r="C213" s="8" t="s">
@@ -15770,10 +15777,10 @@
       </c>
     </row>
     <row r="214" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A214" s="17">
+      <c r="A214" s="16">
         <v>100740</v>
       </c>
-      <c r="B214" s="18">
+      <c r="B214" s="17">
         <v>44341</v>
       </c>
       <c r="C214" s="8" t="s">
@@ -15802,10 +15809,10 @@
       </c>
     </row>
     <row r="215" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A215" s="17">
+      <c r="A215" s="16">
         <v>100757</v>
       </c>
-      <c r="B215" s="18">
+      <c r="B215" s="17">
         <v>44341</v>
       </c>
       <c r="C215" s="8" t="s">
@@ -15834,10 +15841,10 @@
       </c>
     </row>
     <row r="216" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A216" s="17">
+      <c r="A216" s="16">
         <v>100750</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="17">
         <v>44343</v>
       </c>
       <c r="C216" s="8" t="s">
@@ -15866,10 +15873,10 @@
       </c>
     </row>
     <row r="217" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A217" s="17">
+      <c r="A217" s="16">
         <v>100756</v>
       </c>
-      <c r="B217" s="18">
+      <c r="B217" s="17">
         <v>44343</v>
       </c>
       <c r="C217" s="8" t="s">
@@ -15898,10 +15905,10 @@
       </c>
     </row>
     <row r="218" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A218" s="17">
+      <c r="A218" s="16">
         <v>100754</v>
       </c>
-      <c r="B218" s="18">
+      <c r="B218" s="17">
         <v>44345</v>
       </c>
       <c r="C218" s="8" t="s">
@@ -15930,10 +15937,10 @@
       </c>
     </row>
     <row r="219" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A219" s="17">
+      <c r="A219" s="16">
         <v>100764</v>
       </c>
-      <c r="B219" s="18">
+      <c r="B219" s="17">
         <v>44345</v>
       </c>
       <c r="C219" s="8" t="s">
@@ -15962,10 +15969,10 @@
       </c>
     </row>
     <row r="220" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A220" s="17">
+      <c r="A220" s="16">
         <v>100724</v>
       </c>
-      <c r="B220" s="18">
+      <c r="B220" s="17">
         <v>44346</v>
       </c>
       <c r="C220" s="8" t="s">
@@ -15994,10 +16001,10 @@
       </c>
     </row>
     <row r="221" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A221" s="17">
+      <c r="A221" s="16">
         <v>100686</v>
       </c>
-      <c r="B221" s="18">
+      <c r="B221" s="17">
         <v>44348</v>
       </c>
       <c r="C221" s="8" t="s">
@@ -16026,10 +16033,10 @@
       </c>
     </row>
     <row r="222" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A222" s="17">
+      <c r="A222" s="16">
         <v>100761</v>
       </c>
-      <c r="B222" s="18">
+      <c r="B222" s="17">
         <v>44349</v>
       </c>
       <c r="C222" s="8" t="s">
@@ -16058,10 +16065,10 @@
       </c>
     </row>
     <row r="223" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A223" s="17">
+      <c r="A223" s="16">
         <v>100695</v>
       </c>
-      <c r="B223" s="18">
+      <c r="B223" s="17">
         <v>44350</v>
       </c>
       <c r="C223" s="8" t="s">
@@ -16090,10 +16097,10 @@
       </c>
     </row>
     <row r="224" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A224" s="17">
+      <c r="A224" s="16">
         <v>100727</v>
       </c>
-      <c r="B224" s="18">
+      <c r="B224" s="17">
         <v>44350</v>
       </c>
       <c r="C224" s="8" t="s">
@@ -16122,10 +16129,10 @@
       </c>
     </row>
     <row r="225" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A225" s="17">
+      <c r="A225" s="16">
         <v>100777</v>
       </c>
-      <c r="B225" s="18">
+      <c r="B225" s="17">
         <v>44350</v>
       </c>
       <c r="C225" s="8" t="s">
@@ -16154,10 +16161,10 @@
       </c>
     </row>
     <row r="226" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A226" s="17">
+      <c r="A226" s="16">
         <v>100774</v>
       </c>
-      <c r="B226" s="18">
+      <c r="B226" s="17">
         <v>44351</v>
       </c>
       <c r="C226" s="8" t="s">
@@ -16186,10 +16193,10 @@
       </c>
     </row>
     <row r="227" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A227" s="17">
+      <c r="A227" s="16">
         <v>100720</v>
       </c>
-      <c r="B227" s="18">
+      <c r="B227" s="17">
         <v>44352</v>
       </c>
       <c r="C227" s="8" t="s">
@@ -16218,10 +16225,10 @@
       </c>
     </row>
     <row r="228" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A228" s="17">
+      <c r="A228" s="16">
         <v>100723</v>
       </c>
-      <c r="B228" s="18">
+      <c r="B228" s="17">
         <v>44352</v>
       </c>
       <c r="C228" s="8" t="s">
@@ -16250,10 +16257,10 @@
       </c>
     </row>
     <row r="229" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A229" s="17">
+      <c r="A229" s="16">
         <v>100759</v>
       </c>
-      <c r="B229" s="18">
+      <c r="B229" s="17">
         <v>44352</v>
       </c>
       <c r="C229" s="8" t="s">
@@ -16282,10 +16289,10 @@
       </c>
     </row>
     <row r="230" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A230" s="17">
+      <c r="A230" s="16">
         <v>100722</v>
       </c>
-      <c r="B230" s="18">
+      <c r="B230" s="17">
         <v>44353</v>
       </c>
       <c r="C230" s="8" t="s">
@@ -16314,10 +16321,10 @@
       </c>
     </row>
     <row r="231" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A231" s="17">
+      <c r="A231" s="16">
         <v>100731</v>
       </c>
-      <c r="B231" s="18">
+      <c r="B231" s="17">
         <v>44353</v>
       </c>
       <c r="C231" s="8" t="s">
@@ -16346,10 +16353,10 @@
       </c>
     </row>
     <row r="232" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A232" s="17">
+      <c r="A232" s="16">
         <v>100755</v>
       </c>
-      <c r="B232" s="18">
+      <c r="B232" s="17">
         <v>44353</v>
       </c>
       <c r="C232" s="8" t="s">
@@ -16378,10 +16385,10 @@
       </c>
     </row>
     <row r="233" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A233" s="17">
+      <c r="A233" s="16">
         <v>100745</v>
       </c>
-      <c r="B233" s="18">
+      <c r="B233" s="17">
         <v>44354</v>
       </c>
       <c r="C233" s="8" t="s">
@@ -16410,10 +16417,10 @@
       </c>
     </row>
     <row r="234" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A234" s="17">
+      <c r="A234" s="16">
         <v>100746</v>
       </c>
-      <c r="B234" s="18">
+      <c r="B234" s="17">
         <v>44354</v>
       </c>
       <c r="C234" s="8" t="s">
@@ -16442,10 +16449,10 @@
       </c>
     </row>
     <row r="235" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A235" s="17">
+      <c r="A235" s="16">
         <v>100747</v>
       </c>
-      <c r="B235" s="18">
+      <c r="B235" s="17">
         <v>44354</v>
       </c>
       <c r="C235" s="8" t="s">
@@ -16474,10 +16481,10 @@
       </c>
     </row>
     <row r="236" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A236" s="17">
+      <c r="A236" s="16">
         <v>100780</v>
       </c>
-      <c r="B236" s="18">
+      <c r="B236" s="17">
         <v>44355</v>
       </c>
       <c r="C236" s="8" t="s">
@@ -16506,10 +16513,10 @@
       </c>
     </row>
     <row r="237" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A237" s="17">
+      <c r="A237" s="16">
         <v>100760</v>
       </c>
-      <c r="B237" s="18">
+      <c r="B237" s="17">
         <v>44356</v>
       </c>
       <c r="C237" s="8" t="s">
@@ -16538,10 +16545,10 @@
       </c>
     </row>
     <row r="238" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A238" s="17">
+      <c r="A238" s="16">
         <v>100781</v>
       </c>
-      <c r="B238" s="18">
+      <c r="B238" s="17">
         <v>44356</v>
       </c>
       <c r="C238" s="8" t="s">
@@ -16570,10 +16577,10 @@
       </c>
     </row>
     <row r="239" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A239" s="17">
+      <c r="A239" s="16">
         <v>100783</v>
       </c>
-      <c r="B239" s="18">
+      <c r="B239" s="17">
         <v>44356</v>
       </c>
       <c r="C239" s="8" t="s">
@@ -16602,10 +16609,10 @@
       </c>
     </row>
     <row r="240" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A240" s="17">
+      <c r="A240" s="16">
         <v>100768</v>
       </c>
-      <c r="B240" s="18">
+      <c r="B240" s="17">
         <v>44357</v>
       </c>
       <c r="C240" s="8" t="s">
@@ -16634,10 +16641,10 @@
       </c>
     </row>
     <row r="241" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A241" s="17">
+      <c r="A241" s="16">
         <v>100769</v>
       </c>
-      <c r="B241" s="18">
+      <c r="B241" s="17">
         <v>44357</v>
       </c>
       <c r="C241" s="8" t="s">
@@ -16666,10 +16673,10 @@
       </c>
     </row>
     <row r="242" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A242" s="17">
+      <c r="A242" s="16">
         <v>100775</v>
       </c>
-      <c r="B242" s="18">
+      <c r="B242" s="17">
         <v>44357</v>
       </c>
       <c r="C242" s="8" t="s">
@@ -16698,10 +16705,10 @@
       </c>
     </row>
     <row r="243" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A243" s="17">
+      <c r="A243" s="16">
         <v>100773</v>
       </c>
-      <c r="B243" s="18">
+      <c r="B243" s="17">
         <v>44358</v>
       </c>
       <c r="C243" s="8" t="s">
@@ -16730,10 +16737,10 @@
       </c>
     </row>
     <row r="244" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A244" s="17">
+      <c r="A244" s="16">
         <v>100789</v>
       </c>
-      <c r="B244" s="18">
+      <c r="B244" s="17">
         <v>44434</v>
       </c>
       <c r="C244" s="8" t="s">
@@ -16762,10 +16769,10 @@
       </c>
     </row>
     <row r="245" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A245" s="17">
+      <c r="A245" s="16">
         <v>100790</v>
       </c>
-      <c r="B245" s="18">
+      <c r="B245" s="17">
         <v>44434</v>
       </c>
       <c r="C245" s="8" t="s">
@@ -16794,10 +16801,10 @@
       </c>
     </row>
     <row r="246" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A246" s="17">
+      <c r="A246" s="16">
         <v>100792</v>
       </c>
-      <c r="B246" s="18">
+      <c r="B246" s="17">
         <v>44434</v>
       </c>
       <c r="C246" s="8" t="s">
@@ -16826,10 +16833,10 @@
       </c>
     </row>
     <row r="247" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A247" s="17">
+      <c r="A247" s="16">
         <v>100793</v>
       </c>
-      <c r="B247" s="18">
+      <c r="B247" s="17">
         <v>44435</v>
       </c>
       <c r="C247" s="8" t="s">
@@ -16858,10 +16865,10 @@
       </c>
     </row>
     <row r="248" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A248" s="17">
+      <c r="A248" s="16">
         <v>100797</v>
       </c>
-      <c r="B248" s="18">
+      <c r="B248" s="17">
         <v>44437</v>
       </c>
       <c r="C248" s="8" t="s">
@@ -16890,10 +16897,10 @@
       </c>
     </row>
     <row r="249" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A249" s="17">
+      <c r="A249" s="16">
         <v>100799</v>
       </c>
-      <c r="B249" s="18">
+      <c r="B249" s="17">
         <v>44438</v>
       </c>
       <c r="C249" s="8" t="s">
@@ -16922,10 +16929,10 @@
       </c>
     </row>
     <row r="250" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A250" s="17">
+      <c r="A250" s="16">
         <v>100800</v>
       </c>
-      <c r="B250" s="18">
+      <c r="B250" s="17">
         <v>44438</v>
       </c>
       <c r="C250" s="8" t="s">
@@ -16954,10 +16961,10 @@
       </c>
     </row>
     <row r="251" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A251" s="17">
+      <c r="A251" s="16">
         <v>100801</v>
       </c>
-      <c r="B251" s="18">
+      <c r="B251" s="17">
         <v>44439</v>
       </c>
       <c r="C251" s="8" t="s">
@@ -16986,10 +16993,10 @@
       </c>
     </row>
     <row r="252" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A252" s="17">
+      <c r="A252" s="16">
         <v>100803</v>
       </c>
-      <c r="B252" s="18">
+      <c r="B252" s="17">
         <v>44439</v>
       </c>
       <c r="C252" s="8" t="s">
@@ -17018,10 +17025,10 @@
       </c>
     </row>
     <row r="253" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A253" s="17">
+      <c r="A253" s="16">
         <v>100805</v>
       </c>
-      <c r="B253" s="18">
+      <c r="B253" s="17">
         <v>44440</v>
       </c>
       <c r="C253" s="8" t="s">
@@ -17050,10 +17057,10 @@
       </c>
     </row>
     <row r="254" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A254" s="17">
+      <c r="A254" s="16">
         <v>100808</v>
       </c>
-      <c r="B254" s="18">
+      <c r="B254" s="17">
         <v>44441</v>
       </c>
       <c r="C254" s="8" t="s">
@@ -17082,10 +17089,10 @@
       </c>
     </row>
     <row r="255" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A255" s="17">
+      <c r="A255" s="16">
         <v>100810</v>
       </c>
-      <c r="B255" s="18">
+      <c r="B255" s="17">
         <v>44441</v>
       </c>
       <c r="C255" s="8" t="s">
@@ -17114,10 +17121,10 @@
       </c>
     </row>
     <row r="256" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A256" s="17">
+      <c r="A256" s="16">
         <v>100811</v>
       </c>
-      <c r="B256" s="18">
+      <c r="B256" s="17">
         <v>44441</v>
       </c>
       <c r="C256" s="8" t="s">
@@ -17146,10 +17153,10 @@
       </c>
     </row>
     <row r="257" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A257" s="17">
+      <c r="A257" s="16">
         <v>100813</v>
       </c>
-      <c r="B257" s="18">
+      <c r="B257" s="17">
         <v>44441</v>
       </c>
       <c r="C257" s="8" t="s">
@@ -17178,10 +17185,10 @@
       </c>
     </row>
     <row r="258" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A258" s="17">
+      <c r="A258" s="16">
         <v>100814</v>
       </c>
-      <c r="B258" s="18">
+      <c r="B258" s="17">
         <v>44441</v>
       </c>
       <c r="C258" s="8" t="s">
@@ -17210,10 +17217,10 @@
       </c>
     </row>
     <row r="259" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A259" s="17">
+      <c r="A259" s="16">
         <v>100817</v>
       </c>
-      <c r="B259" s="18">
+      <c r="B259" s="17">
         <v>44442</v>
       </c>
       <c r="C259" s="8" t="s">
@@ -17242,10 +17249,10 @@
       </c>
     </row>
     <row r="260" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A260" s="17">
+      <c r="A260" s="16">
         <v>100818</v>
       </c>
-      <c r="B260" s="18">
+      <c r="B260" s="17">
         <v>44442</v>
       </c>
       <c r="C260" s="8" t="s">
@@ -17274,10 +17281,10 @@
       </c>
     </row>
     <row r="261" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A261" s="17">
+      <c r="A261" s="16">
         <v>100819</v>
       </c>
-      <c r="B261" s="18">
+      <c r="B261" s="17">
         <v>44444</v>
       </c>
       <c r="C261" s="8" t="s">
@@ -17306,10 +17313,10 @@
       </c>
     </row>
     <row r="262" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A262" s="17">
+      <c r="A262" s="16">
         <v>100821</v>
       </c>
-      <c r="B262" s="18">
+      <c r="B262" s="17">
         <v>44444</v>
       </c>
       <c r="C262" s="8" t="s">
@@ -17338,10 +17345,10 @@
       </c>
     </row>
     <row r="263" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A263" s="17">
+      <c r="A263" s="16">
         <v>100822</v>
       </c>
-      <c r="B263" s="18">
+      <c r="B263" s="17">
         <v>44445</v>
       </c>
       <c r="C263" s="8" t="s">
@@ -17370,10 +17377,10 @@
       </c>
     </row>
     <row r="264" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A264" s="17">
+      <c r="A264" s="16">
         <v>100823</v>
       </c>
-      <c r="B264" s="18">
+      <c r="B264" s="17">
         <v>44445</v>
       </c>
       <c r="C264" s="8" t="s">
@@ -17402,10 +17409,10 @@
       </c>
     </row>
     <row r="265" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A265" s="17">
+      <c r="A265" s="16">
         <v>100824</v>
       </c>
-      <c r="B265" s="18">
+      <c r="B265" s="17">
         <v>44446</v>
       </c>
       <c r="C265" s="8" t="s">
@@ -17434,10 +17441,10 @@
       </c>
     </row>
     <row r="266" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A266" s="17">
+      <c r="A266" s="16">
         <v>100825</v>
       </c>
-      <c r="B266" s="18">
+      <c r="B266" s="17">
         <v>44446</v>
       </c>
       <c r="C266" s="8" t="s">
@@ -17466,10 +17473,10 @@
       </c>
     </row>
     <row r="267" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A267" s="17">
+      <c r="A267" s="16">
         <v>100826</v>
       </c>
-      <c r="B267" s="18">
+      <c r="B267" s="17">
         <v>44446</v>
       </c>
       <c r="C267" s="8" t="s">
@@ -17498,10 +17505,10 @@
       </c>
     </row>
     <row r="268" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A268" s="17">
+      <c r="A268" s="16">
         <v>100828</v>
       </c>
-      <c r="B268" s="18">
+      <c r="B268" s="17">
         <v>44448</v>
       </c>
       <c r="C268" s="8" t="s">
@@ -17530,10 +17537,10 @@
       </c>
     </row>
     <row r="269" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A269" s="17">
+      <c r="A269" s="16">
         <v>100831</v>
       </c>
-      <c r="B269" s="18">
+      <c r="B269" s="17">
         <v>44449</v>
       </c>
       <c r="C269" s="8" t="s">
@@ -17562,10 +17569,10 @@
       </c>
     </row>
     <row r="270" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A270" s="17">
+      <c r="A270" s="16">
         <v>100832</v>
       </c>
-      <c r="B270" s="18">
+      <c r="B270" s="17">
         <v>44449</v>
       </c>
       <c r="C270" s="8" t="s">
@@ -17594,10 +17601,10 @@
       </c>
     </row>
     <row r="271" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A271" s="17">
+      <c r="A271" s="16">
         <v>100834</v>
       </c>
-      <c r="B271" s="18">
+      <c r="B271" s="17">
         <v>44450</v>
       </c>
       <c r="C271" s="8" t="s">
@@ -17626,10 +17633,10 @@
       </c>
     </row>
     <row r="272" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A272" s="17">
+      <c r="A272" s="16">
         <v>100836</v>
       </c>
-      <c r="B272" s="18">
+      <c r="B272" s="17">
         <v>44450</v>
       </c>
       <c r="C272" s="8" t="s">
@@ -17658,10 +17665,10 @@
       </c>
     </row>
     <row r="273" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A273" s="17">
+      <c r="A273" s="16">
         <v>100837</v>
       </c>
-      <c r="B273" s="18">
+      <c r="B273" s="17">
         <v>44450</v>
       </c>
       <c r="C273" s="8" t="s">
@@ -17690,10 +17697,10 @@
       </c>
     </row>
     <row r="274" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A274" s="17">
+      <c r="A274" s="16">
         <v>100838</v>
       </c>
-      <c r="B274" s="18">
+      <c r="B274" s="17">
         <v>44450</v>
       </c>
       <c r="C274" s="8" t="s">
@@ -17722,10 +17729,10 @@
       </c>
     </row>
     <row r="275" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A275" s="17">
+      <c r="A275" s="16">
         <v>100839</v>
       </c>
-      <c r="B275" s="18">
+      <c r="B275" s="17">
         <v>44452</v>
       </c>
       <c r="C275" s="8" t="s">
@@ -17754,10 +17761,10 @@
       </c>
     </row>
     <row r="276" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A276" s="17">
+      <c r="A276" s="16">
         <v>100844</v>
       </c>
-      <c r="B276" s="18">
+      <c r="B276" s="17">
         <v>44454</v>
       </c>
       <c r="C276" s="8" t="s">
@@ -17786,10 +17793,10 @@
       </c>
     </row>
     <row r="277" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A277" s="17">
+      <c r="A277" s="16">
         <v>100845</v>
       </c>
-      <c r="B277" s="18">
+      <c r="B277" s="17">
         <v>44454</v>
       </c>
       <c r="C277" s="8" t="s">
@@ -17818,10 +17825,10 @@
       </c>
     </row>
     <row r="278" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A278" s="17">
+      <c r="A278" s="16">
         <v>100846</v>
       </c>
-      <c r="B278" s="18">
+      <c r="B278" s="17">
         <v>44454</v>
       </c>
       <c r="C278" s="8" t="s">
@@ -17850,10 +17857,10 @@
       </c>
     </row>
     <row r="279" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A279" s="17">
+      <c r="A279" s="16">
         <v>100850</v>
       </c>
-      <c r="B279" s="18">
+      <c r="B279" s="17">
         <v>44455</v>
       </c>
       <c r="C279" s="8" t="s">
@@ -17882,10 +17889,10 @@
       </c>
     </row>
     <row r="280" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A280" s="17">
+      <c r="A280" s="16">
         <v>100854</v>
       </c>
-      <c r="B280" s="18">
+      <c r="B280" s="17">
         <v>44460</v>
       </c>
       <c r="C280" s="8" t="s">
@@ -17914,10 +17921,10 @@
       </c>
     </row>
     <row r="281" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A281" s="17">
+      <c r="A281" s="16">
         <v>100856</v>
       </c>
-      <c r="B281" s="18">
+      <c r="B281" s="17">
         <v>44461</v>
       </c>
       <c r="C281" s="8" t="s">
@@ -17946,10 +17953,10 @@
       </c>
     </row>
     <row r="282" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A282" s="17">
+      <c r="A282" s="16">
         <v>100857</v>
       </c>
-      <c r="B282" s="18">
+      <c r="B282" s="17">
         <v>44462</v>
       </c>
       <c r="C282" s="8" t="s">
@@ -17978,10 +17985,10 @@
       </c>
     </row>
     <row r="283" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A283" s="17">
+      <c r="A283" s="16">
         <v>100859</v>
       </c>
-      <c r="B283" s="18">
+      <c r="B283" s="17">
         <v>44462</v>
       </c>
       <c r="C283" s="8" t="s">
@@ -18010,10 +18017,10 @@
       </c>
     </row>
     <row r="284" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A284" s="17">
+      <c r="A284" s="16">
         <v>100861</v>
       </c>
-      <c r="B284" s="18">
+      <c r="B284" s="17">
         <v>44462</v>
       </c>
       <c r="C284" s="8" t="s">
@@ -18042,10 +18049,10 @@
       </c>
     </row>
     <row r="285" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A285" s="17">
+      <c r="A285" s="16">
         <v>100863</v>
       </c>
-      <c r="B285" s="18">
+      <c r="B285" s="17">
         <v>44463</v>
       </c>
       <c r="C285" s="8" t="s">
@@ -18074,10 +18081,10 @@
       </c>
     </row>
     <row r="286" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A286" s="17">
+      <c r="A286" s="16">
         <v>100864</v>
       </c>
-      <c r="B286" s="18">
+      <c r="B286" s="17">
         <v>44463</v>
       </c>
       <c r="C286" s="8" t="s">
@@ -18106,10 +18113,10 @@
       </c>
     </row>
     <row r="287" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A287" s="17">
+      <c r="A287" s="16">
         <v>100868</v>
       </c>
-      <c r="B287" s="18">
+      <c r="B287" s="17">
         <v>44465</v>
       </c>
       <c r="C287" s="8" t="s">
@@ -18138,10 +18145,10 @@
       </c>
     </row>
     <row r="288" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A288" s="17">
+      <c r="A288" s="16">
         <v>100869</v>
       </c>
-      <c r="B288" s="18">
+      <c r="B288" s="17">
         <v>44465</v>
       </c>
       <c r="C288" s="8" t="s">
@@ -18170,10 +18177,10 @@
       </c>
     </row>
     <row r="289" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A289" s="17">
+      <c r="A289" s="16">
         <v>100870</v>
       </c>
-      <c r="B289" s="18">
+      <c r="B289" s="17">
         <v>44466</v>
       </c>
       <c r="C289" s="8" t="s">
@@ -18202,10 +18209,10 @@
       </c>
     </row>
     <row r="290" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A290" s="17">
+      <c r="A290" s="16">
         <v>100872</v>
       </c>
-      <c r="B290" s="18">
+      <c r="B290" s="17">
         <v>44467</v>
       </c>
       <c r="C290" s="8" t="s">
@@ -18234,10 +18241,10 @@
       </c>
     </row>
     <row r="291" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A291" s="17">
+      <c r="A291" s="16">
         <v>100873</v>
       </c>
-      <c r="B291" s="18">
+      <c r="B291" s="17">
         <v>44468</v>
       </c>
       <c r="C291" s="8" t="s">
@@ -18266,10 +18273,10 @@
       </c>
     </row>
     <row r="292" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A292" s="17">
+      <c r="A292" s="16">
         <v>100874</v>
       </c>
-      <c r="B292" s="18">
+      <c r="B292" s="17">
         <v>44469</v>
       </c>
       <c r="C292" s="8" t="s">
@@ -18298,10 +18305,10 @@
       </c>
     </row>
     <row r="293" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A293" s="17">
+      <c r="A293" s="16">
         <v>100875</v>
       </c>
-      <c r="B293" s="18">
+      <c r="B293" s="17">
         <v>44470</v>
       </c>
       <c r="C293" s="8" t="s">
@@ -18330,10 +18337,10 @@
       </c>
     </row>
     <row r="294" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A294" s="17">
+      <c r="A294" s="16">
         <v>100876</v>
       </c>
-      <c r="B294" s="18">
+      <c r="B294" s="17">
         <v>44470</v>
       </c>
       <c r="C294" s="8" t="s">
@@ -18362,10 +18369,10 @@
       </c>
     </row>
     <row r="295" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A295" s="17">
+      <c r="A295" s="16">
         <v>100878</v>
       </c>
-      <c r="B295" s="18">
+      <c r="B295" s="17">
         <v>44470</v>
       </c>
       <c r="C295" s="8" t="s">
@@ -18394,10 +18401,10 @@
       </c>
     </row>
     <row r="296" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A296" s="17">
+      <c r="A296" s="16">
         <v>100882</v>
       </c>
-      <c r="B296" s="18">
+      <c r="B296" s="17">
         <v>44472</v>
       </c>
       <c r="C296" s="8" t="s">
@@ -18426,10 +18433,10 @@
       </c>
     </row>
     <row r="297" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A297" s="17">
+      <c r="A297" s="16">
         <v>100883</v>
       </c>
-      <c r="B297" s="18">
+      <c r="B297" s="17">
         <v>44473</v>
       </c>
       <c r="C297" s="8" t="s">
@@ -18458,10 +18465,10 @@
       </c>
     </row>
     <row r="298" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A298" s="17">
+      <c r="A298" s="16">
         <v>100885</v>
       </c>
-      <c r="B298" s="18">
+      <c r="B298" s="17">
         <v>44473</v>
       </c>
       <c r="C298" s="8" t="s">
@@ -18490,10 +18497,10 @@
       </c>
     </row>
     <row r="299" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A299" s="17">
+      <c r="A299" s="16">
         <v>100886</v>
       </c>
-      <c r="B299" s="18">
+      <c r="B299" s="17">
         <v>44473</v>
       </c>
       <c r="C299" s="8" t="s">
@@ -18522,10 +18529,10 @@
       </c>
     </row>
     <row r="300" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A300" s="17">
+      <c r="A300" s="16">
         <v>100887</v>
       </c>
-      <c r="B300" s="18">
+      <c r="B300" s="17">
         <v>44474</v>
       </c>
       <c r="C300" s="8" t="s">
@@ -18554,10 +18561,10 @@
       </c>
     </row>
     <row r="301" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A301" s="17">
+      <c r="A301" s="16">
         <v>100889</v>
       </c>
-      <c r="B301" s="18">
+      <c r="B301" s="17">
         <v>44474</v>
       </c>
       <c r="C301" s="8" t="s">
@@ -18586,10 +18593,10 @@
       </c>
     </row>
     <row r="302" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A302" s="17">
+      <c r="A302" s="16">
         <v>100894</v>
       </c>
-      <c r="B302" s="18">
+      <c r="B302" s="17">
         <v>44476</v>
       </c>
       <c r="C302" s="8" t="s">
@@ -18618,10 +18625,10 @@
       </c>
     </row>
     <row r="303" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A303" s="17">
+      <c r="A303" s="16">
         <v>100895</v>
       </c>
-      <c r="B303" s="18">
+      <c r="B303" s="17">
         <v>44476</v>
       </c>
       <c r="C303" s="8" t="s">
@@ -18650,10 +18657,10 @@
       </c>
     </row>
     <row r="304" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A304" s="17">
+      <c r="A304" s="16">
         <v>100898</v>
       </c>
-      <c r="B304" s="18">
+      <c r="B304" s="17">
         <v>44479</v>
       </c>
       <c r="C304" s="8" t="s">
@@ -18682,10 +18689,10 @@
       </c>
     </row>
     <row r="305" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A305" s="17">
+      <c r="A305" s="16">
         <v>100900</v>
       </c>
-      <c r="B305" s="18">
+      <c r="B305" s="17">
         <v>44480</v>
       </c>
       <c r="C305" s="8" t="s">
@@ -18714,10 +18721,10 @@
       </c>
     </row>
     <row r="306" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A306" s="17">
+      <c r="A306" s="16">
         <v>100901</v>
       </c>
-      <c r="B306" s="18">
+      <c r="B306" s="17">
         <v>44480</v>
       </c>
       <c r="C306" s="8" t="s">
@@ -18746,10 +18753,10 @@
       </c>
     </row>
     <row r="307" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A307" s="17">
+      <c r="A307" s="16">
         <v>100903</v>
       </c>
-      <c r="B307" s="18">
+      <c r="B307" s="17">
         <v>44481</v>
       </c>
       <c r="C307" s="8" t="s">
@@ -18778,10 +18785,10 @@
       </c>
     </row>
     <row r="308" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A308" s="17">
+      <c r="A308" s="16">
         <v>100904</v>
       </c>
-      <c r="B308" s="18">
+      <c r="B308" s="17">
         <v>44482</v>
       </c>
       <c r="C308" s="8" t="s">
@@ -18810,10 +18817,10 @@
       </c>
     </row>
     <row r="309" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A309" s="17">
+      <c r="A309" s="16">
         <v>100908</v>
       </c>
-      <c r="B309" s="18">
+      <c r="B309" s="17">
         <v>44483</v>
       </c>
       <c r="C309" s="8" t="s">
@@ -18842,10 +18849,10 @@
       </c>
     </row>
     <row r="310" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A310" s="17">
+      <c r="A310" s="16">
         <v>100909</v>
       </c>
-      <c r="B310" s="18">
+      <c r="B310" s="17">
         <v>44483</v>
       </c>
       <c r="C310" s="8" t="s">
@@ -18874,10 +18881,10 @@
       </c>
     </row>
     <row r="311" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A311" s="17">
+      <c r="A311" s="16">
         <v>100910</v>
       </c>
-      <c r="B311" s="18">
+      <c r="B311" s="17">
         <v>44483</v>
       </c>
       <c r="C311" s="8" t="s">
@@ -18906,10 +18913,10 @@
       </c>
     </row>
     <row r="312" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A312" s="17">
+      <c r="A312" s="16">
         <v>100912</v>
       </c>
-      <c r="B312" s="18">
+      <c r="B312" s="17">
         <v>44484</v>
       </c>
       <c r="C312" s="8" t="s">
@@ -18938,10 +18945,10 @@
       </c>
     </row>
     <row r="313" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A313" s="17">
+      <c r="A313" s="16">
         <v>100215</v>
       </c>
-      <c r="B313" s="18">
+      <c r="B313" s="17">
         <v>44486</v>
       </c>
       <c r="C313" s="8" t="s">
@@ -18970,10 +18977,10 @@
       </c>
     </row>
     <row r="314" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A314" s="17">
+      <c r="A314" s="16">
         <v>100914</v>
       </c>
-      <c r="B314" s="18">
+      <c r="B314" s="17">
         <v>44486</v>
       </c>
       <c r="C314" s="8" t="s">
@@ -19002,10 +19009,10 @@
       </c>
     </row>
     <row r="315" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A315" s="17">
+      <c r="A315" s="16">
         <v>100916</v>
       </c>
-      <c r="B315" s="18">
+      <c r="B315" s="17">
         <v>44487</v>
       </c>
       <c r="C315" s="8" t="s">
@@ -19034,10 +19041,10 @@
       </c>
     </row>
     <row r="316" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A316" s="17">
+      <c r="A316" s="16">
         <v>100919</v>
       </c>
-      <c r="B316" s="18">
+      <c r="B316" s="17">
         <v>44489</v>
       </c>
       <c r="C316" s="8" t="s">
@@ -19066,10 +19073,10 @@
       </c>
     </row>
     <row r="317" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A317" s="17">
+      <c r="A317" s="16">
         <v>100920</v>
       </c>
-      <c r="B317" s="18">
+      <c r="B317" s="17">
         <v>44489</v>
       </c>
       <c r="C317" s="8" t="s">
@@ -19098,10 +19105,10 @@
       </c>
     </row>
     <row r="318" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A318" s="17">
+      <c r="A318" s="16">
         <v>100228</v>
       </c>
-      <c r="B318" s="18">
+      <c r="B318" s="17">
         <v>44490</v>
       </c>
       <c r="C318" s="8" t="s">
@@ -19130,10 +19137,10 @@
       </c>
     </row>
     <row r="319" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A319" s="17">
+      <c r="A319" s="16">
         <v>100923</v>
       </c>
-      <c r="B319" s="18">
+      <c r="B319" s="17">
         <v>44490</v>
       </c>
       <c r="C319" s="8" t="s">
@@ -19162,10 +19169,10 @@
       </c>
     </row>
     <row r="320" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A320" s="17">
+      <c r="A320" s="16">
         <v>100927</v>
       </c>
-      <c r="B320" s="18">
+      <c r="B320" s="17">
         <v>44491</v>
       </c>
       <c r="C320" s="8" t="s">
@@ -19194,10 +19201,10 @@
       </c>
     </row>
     <row r="321" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A321" s="17">
+      <c r="A321" s="16">
         <v>100928</v>
       </c>
-      <c r="B321" s="18">
+      <c r="B321" s="17">
         <v>44491</v>
       </c>
       <c r="C321" s="8" t="s">
@@ -19226,10 +19233,10 @@
       </c>
     </row>
     <row r="322" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A322" s="17">
+      <c r="A322" s="16">
         <v>100929</v>
       </c>
-      <c r="B322" s="18">
+      <c r="B322" s="17">
         <v>44491</v>
       </c>
       <c r="C322" s="8" t="s">
@@ -19258,10 +19265,10 @@
       </c>
     </row>
     <row r="323" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A323" s="17">
+      <c r="A323" s="16">
         <v>100214</v>
       </c>
-      <c r="B323" s="18">
+      <c r="B323" s="17">
         <v>44492</v>
       </c>
       <c r="C323" s="8" t="s">
@@ -19290,10 +19297,10 @@
       </c>
     </row>
     <row r="324" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A324" s="17">
+      <c r="A324" s="16">
         <v>100932</v>
       </c>
-      <c r="B324" s="18">
+      <c r="B324" s="17">
         <v>44492</v>
       </c>
       <c r="C324" s="8" t="s">
@@ -19322,10 +19329,10 @@
       </c>
     </row>
     <row r="325" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A325" s="17">
+      <c r="A325" s="16">
         <v>100933</v>
       </c>
-      <c r="B325" s="18">
+      <c r="B325" s="17">
         <v>44492</v>
       </c>
       <c r="C325" s="8" t="s">
@@ -19354,10 +19361,10 @@
       </c>
     </row>
     <row r="326" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A326" s="17">
+      <c r="A326" s="16">
         <v>100934</v>
       </c>
-      <c r="B326" s="18">
+      <c r="B326" s="17">
         <v>44493</v>
       </c>
       <c r="C326" s="8" t="s">
@@ -19386,10 +19393,10 @@
       </c>
     </row>
     <row r="327" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A327" s="17">
+      <c r="A327" s="16">
         <v>100936</v>
       </c>
-      <c r="B327" s="18">
+      <c r="B327" s="17">
         <v>44495</v>
       </c>
       <c r="C327" s="8" t="s">
@@ -19418,10 +19425,10 @@
       </c>
     </row>
     <row r="328" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A328" s="17">
+      <c r="A328" s="16">
         <v>100250</v>
       </c>
-      <c r="B328" s="18">
+      <c r="B328" s="17">
         <v>44496</v>
       </c>
       <c r="C328" s="8" t="s">
@@ -19450,10 +19457,10 @@
       </c>
     </row>
     <row r="329" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A329" s="17">
+      <c r="A329" s="16">
         <v>100939</v>
       </c>
-      <c r="B329" s="18">
+      <c r="B329" s="17">
         <v>44496</v>
       </c>
       <c r="C329" s="8" t="s">
@@ -19482,10 +19489,10 @@
       </c>
     </row>
     <row r="330" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A330" s="17">
+      <c r="A330" s="16">
         <v>100940</v>
       </c>
-      <c r="B330" s="18">
+      <c r="B330" s="17">
         <v>44497</v>
       </c>
       <c r="C330" s="8" t="s">
@@ -19514,10 +19521,10 @@
       </c>
     </row>
     <row r="331" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A331" s="17">
+      <c r="A331" s="16">
         <v>100941</v>
       </c>
-      <c r="B331" s="18">
+      <c r="B331" s="17">
         <v>44497</v>
       </c>
       <c r="C331" s="8" t="s">
@@ -19546,10 +19553,10 @@
       </c>
     </row>
     <row r="332" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A332" s="17">
+      <c r="A332" s="16">
         <v>100942</v>
       </c>
-      <c r="B332" s="18">
+      <c r="B332" s="17">
         <v>44497</v>
       </c>
       <c r="C332" s="8" t="s">
@@ -19578,10 +19585,10 @@
       </c>
     </row>
     <row r="333" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A333" s="17">
+      <c r="A333" s="16">
         <v>100943</v>
       </c>
-      <c r="B333" s="18">
+      <c r="B333" s="17">
         <v>44497</v>
       </c>
       <c r="C333" s="8" t="s">
@@ -19610,10 +19617,10 @@
       </c>
     </row>
     <row r="334" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A334" s="17">
+      <c r="A334" s="16">
         <v>100227</v>
       </c>
-      <c r="B334" s="18">
+      <c r="B334" s="17">
         <v>44498</v>
       </c>
       <c r="C334" s="8" t="s">
@@ -19642,10 +19649,10 @@
       </c>
     </row>
     <row r="335" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A335" s="17">
+      <c r="A335" s="16">
         <v>100945</v>
       </c>
-      <c r="B335" s="18">
+      <c r="B335" s="17">
         <v>44498</v>
       </c>
       <c r="C335" s="8" t="s">
@@ -19674,10 +19681,10 @@
       </c>
     </row>
     <row r="336" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A336" s="17">
+      <c r="A336" s="16">
         <v>100947</v>
       </c>
-      <c r="B336" s="18">
+      <c r="B336" s="17">
         <v>44498</v>
       </c>
       <c r="C336" s="8" t="s">
@@ -19706,10 +19713,10 @@
       </c>
     </row>
     <row r="337" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A337" s="17">
+      <c r="A337" s="16">
         <v>100226</v>
       </c>
-      <c r="B337" s="18">
+      <c r="B337" s="17">
         <v>44499</v>
       </c>
       <c r="C337" s="8" t="s">
@@ -19738,10 +19745,10 @@
       </c>
     </row>
     <row r="338" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A338" s="17">
+      <c r="A338" s="16">
         <v>100948</v>
       </c>
-      <c r="B338" s="18">
+      <c r="B338" s="17">
         <v>44499</v>
       </c>
       <c r="C338" s="8" t="s">
@@ -19770,10 +19777,10 @@
       </c>
     </row>
     <row r="339" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A339" s="17">
+      <c r="A339" s="16">
         <v>100950</v>
       </c>
-      <c r="B339" s="18">
+      <c r="B339" s="17">
         <v>44500</v>
       </c>
       <c r="C339" s="8" t="s">
@@ -19802,10 +19809,10 @@
       </c>
     </row>
     <row r="340" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A340" s="17">
+      <c r="A340" s="16">
         <v>100249</v>
       </c>
-      <c r="B340" s="18">
+      <c r="B340" s="17">
         <v>44501</v>
       </c>
       <c r="C340" s="8" t="s">
@@ -19834,10 +19841,10 @@
       </c>
     </row>
     <row r="341" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A341" s="17">
+      <c r="A341" s="16">
         <v>100952</v>
       </c>
-      <c r="B341" s="18">
+      <c r="B341" s="17">
         <v>44501</v>
       </c>
       <c r="C341" s="8" t="s">
@@ -19866,10 +19873,10 @@
       </c>
     </row>
     <row r="342" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A342" s="17">
+      <c r="A342" s="16">
         <v>100953</v>
       </c>
-      <c r="B342" s="18">
+      <c r="B342" s="17">
         <v>44501</v>
       </c>
       <c r="C342" s="8" t="s">
@@ -19898,10 +19905,10 @@
       </c>
     </row>
     <row r="343" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A343" s="17">
+      <c r="A343" s="16">
         <v>100955</v>
       </c>
-      <c r="B343" s="18">
+      <c r="B343" s="17">
         <v>44503</v>
       </c>
       <c r="C343" s="8" t="s">
@@ -19930,10 +19937,10 @@
       </c>
     </row>
     <row r="344" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A344" s="17">
+      <c r="A344" s="16">
         <v>100287</v>
       </c>
-      <c r="B344" s="18">
+      <c r="B344" s="17">
         <v>44504</v>
       </c>
       <c r="C344" s="8" t="s">
@@ -19962,10 +19969,10 @@
       </c>
     </row>
     <row r="345" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A345" s="17">
+      <c r="A345" s="16">
         <v>100956</v>
       </c>
-      <c r="B345" s="18">
+      <c r="B345" s="17">
         <v>44504</v>
       </c>
       <c r="C345" s="8" t="s">
@@ -19994,10 +20001,10 @@
       </c>
     </row>
     <row r="346" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A346" s="17">
+      <c r="A346" s="16">
         <v>100959</v>
       </c>
-      <c r="B346" s="18">
+      <c r="B346" s="17">
         <v>44505</v>
       </c>
       <c r="C346" s="8" t="s">
@@ -20026,10 +20033,10 @@
       </c>
     </row>
     <row r="347" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A347" s="17">
+      <c r="A347" s="16">
         <v>100261</v>
       </c>
-      <c r="B347" s="18">
+      <c r="B347" s="17">
         <v>44506</v>
       </c>
       <c r="C347" s="8" t="s">
@@ -20058,10 +20065,10 @@
       </c>
     </row>
     <row r="348" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A348" s="17">
+      <c r="A348" s="16">
         <v>100961</v>
       </c>
-      <c r="B348" s="18">
+      <c r="B348" s="17">
         <v>44506</v>
       </c>
       <c r="C348" s="8" t="s">
@@ -20090,10 +20097,10 @@
       </c>
     </row>
     <row r="349" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A349" s="17">
+      <c r="A349" s="16">
         <v>100962</v>
       </c>
-      <c r="B349" s="18">
+      <c r="B349" s="17">
         <v>44507</v>
       </c>
       <c r="C349" s="8" t="s">
@@ -20122,10 +20129,10 @@
       </c>
     </row>
     <row r="350" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A350" s="17">
+      <c r="A350" s="16">
         <v>100966</v>
       </c>
-      <c r="B350" s="18">
+      <c r="B350" s="17">
         <v>44507</v>
       </c>
       <c r="C350" s="8" t="s">
@@ -20154,10 +20161,10 @@
       </c>
     </row>
     <row r="351" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A351" s="17">
+      <c r="A351" s="16">
         <v>100969</v>
       </c>
-      <c r="B351" s="18">
+      <c r="B351" s="17">
         <v>44509</v>
       </c>
       <c r="C351" s="8" t="s">
@@ -20186,10 +20193,10 @@
       </c>
     </row>
     <row r="352" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A352" s="17">
+      <c r="A352" s="16">
         <v>100972</v>
       </c>
-      <c r="B352" s="18">
+      <c r="B352" s="17">
         <v>44509</v>
       </c>
       <c r="C352" s="8" t="s">
@@ -20218,10 +20225,10 @@
       </c>
     </row>
     <row r="353" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A353" s="17">
+      <c r="A353" s="16">
         <v>100974</v>
       </c>
-      <c r="B353" s="18">
+      <c r="B353" s="17">
         <v>44510</v>
       </c>
       <c r="C353" s="8" t="s">
@@ -20250,10 +20257,10 @@
       </c>
     </row>
     <row r="354" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A354" s="17">
+      <c r="A354" s="16">
         <v>100975</v>
       </c>
-      <c r="B354" s="18">
+      <c r="B354" s="17">
         <v>44510</v>
       </c>
       <c r="C354" s="8" t="s">
@@ -20282,10 +20289,10 @@
       </c>
     </row>
     <row r="355" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A355" s="17">
+      <c r="A355" s="16">
         <v>100977</v>
       </c>
-      <c r="B355" s="18">
+      <c r="B355" s="17">
         <v>44510</v>
       </c>
       <c r="C355" s="8" t="s">
@@ -20314,10 +20321,10 @@
       </c>
     </row>
     <row r="356" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A356" s="17">
+      <c r="A356" s="16">
         <v>100978</v>
       </c>
-      <c r="B356" s="18">
+      <c r="B356" s="17">
         <v>44510</v>
       </c>
       <c r="C356" s="8" t="s">
@@ -20346,10 +20353,10 @@
       </c>
     </row>
     <row r="357" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A357" s="17">
+      <c r="A357" s="16">
         <v>100981</v>
       </c>
-      <c r="B357" s="18">
+      <c r="B357" s="17">
         <v>44510</v>
       </c>
       <c r="C357" s="8" t="s">
@@ -20378,10 +20385,10 @@
       </c>
     </row>
     <row r="358" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A358" s="17">
+      <c r="A358" s="16">
         <v>100240</v>
       </c>
-      <c r="B358" s="18">
+      <c r="B358" s="17">
         <v>44511</v>
       </c>
       <c r="C358" s="8" t="s">
@@ -20410,10 +20417,10 @@
       </c>
     </row>
     <row r="359" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A359" s="17">
+      <c r="A359" s="16">
         <v>100982</v>
       </c>
-      <c r="B359" s="18">
+      <c r="B359" s="17">
         <v>44511</v>
       </c>
       <c r="C359" s="8" t="s">
@@ -20442,10 +20449,10 @@
       </c>
     </row>
     <row r="360" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A360" s="17">
+      <c r="A360" s="16">
         <v>100983</v>
       </c>
-      <c r="B360" s="18">
+      <c r="B360" s="17">
         <v>44511</v>
       </c>
       <c r="C360" s="8" t="s">
@@ -20474,10 +20481,10 @@
       </c>
     </row>
     <row r="361" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A361" s="17">
+      <c r="A361" s="16">
         <v>100239</v>
       </c>
-      <c r="B361" s="18">
+      <c r="B361" s="17">
         <v>44512</v>
       </c>
       <c r="C361" s="8" t="s">
@@ -20506,10 +20513,10 @@
       </c>
     </row>
     <row r="362" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A362" s="17">
+      <c r="A362" s="16">
         <v>100985</v>
       </c>
-      <c r="B362" s="18">
+      <c r="B362" s="17">
         <v>44512</v>
       </c>
       <c r="C362" s="8" t="s">
@@ -20538,10 +20545,10 @@
       </c>
     </row>
     <row r="363" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A363" s="17">
+      <c r="A363" s="16">
         <v>100237</v>
       </c>
-      <c r="B363" s="18">
+      <c r="B363" s="17">
         <v>44513</v>
       </c>
       <c r="C363" s="8" t="s">
@@ -20570,10 +20577,10 @@
       </c>
     </row>
     <row r="364" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A364" s="17">
+      <c r="A364" s="16">
         <v>100238</v>
       </c>
-      <c r="B364" s="18">
+      <c r="B364" s="17">
         <v>44513</v>
       </c>
       <c r="C364" s="8" t="s">
@@ -20602,10 +20609,10 @@
       </c>
     </row>
     <row r="365" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A365" s="17">
+      <c r="A365" s="16">
         <v>100986</v>
       </c>
-      <c r="B365" s="18">
+      <c r="B365" s="17">
         <v>44513</v>
       </c>
       <c r="C365" s="8" t="s">
@@ -20634,10 +20641,10 @@
       </c>
     </row>
     <row r="366" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A366" s="17">
+      <c r="A366" s="16">
         <v>100987</v>
       </c>
-      <c r="B366" s="18">
+      <c r="B366" s="17">
         <v>44513</v>
       </c>
       <c r="C366" s="8" t="s">
@@ -20666,10 +20673,10 @@
       </c>
     </row>
     <row r="367" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A367" s="17">
+      <c r="A367" s="16">
         <v>100988</v>
       </c>
-      <c r="B367" s="18">
+      <c r="B367" s="17">
         <v>44513</v>
       </c>
       <c r="C367" s="8" t="s">
@@ -20698,10 +20705,10 @@
       </c>
     </row>
     <row r="368" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A368" s="17">
+      <c r="A368" s="16">
         <v>100260</v>
       </c>
-      <c r="B368" s="18">
+      <c r="B368" s="17">
         <v>44514</v>
       </c>
       <c r="C368" s="8" t="s">
@@ -20730,10 +20737,10 @@
       </c>
     </row>
     <row r="369" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A369" s="17">
+      <c r="A369" s="16">
         <v>100302</v>
       </c>
-      <c r="B369" s="18">
+      <c r="B369" s="17">
         <v>44514</v>
       </c>
       <c r="C369" s="8" t="s">
@@ -20762,10 +20769,10 @@
       </c>
     </row>
     <row r="370" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A370" s="17">
+      <c r="A370" s="16">
         <v>100274</v>
       </c>
-      <c r="B370" s="18">
+      <c r="B370" s="17">
         <v>44515</v>
       </c>
       <c r="C370" s="8" t="s">
@@ -20794,10 +20801,10 @@
       </c>
     </row>
     <row r="371" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A371" s="17">
+      <c r="A371" s="16">
         <v>100209</v>
       </c>
-      <c r="B371" s="18">
+      <c r="B371" s="17">
         <v>44516</v>
       </c>
       <c r="C371" s="8" t="s">
@@ -20826,10 +20833,10 @@
       </c>
     </row>
     <row r="372" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A372" s="17">
+      <c r="A372" s="16">
         <v>100991</v>
       </c>
-      <c r="B372" s="18">
+      <c r="B372" s="17">
         <v>44516</v>
       </c>
       <c r="C372" s="8" t="s">
@@ -20858,10 +20865,10 @@
       </c>
     </row>
     <row r="373" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A373" s="17">
+      <c r="A373" s="16">
         <v>100992</v>
       </c>
-      <c r="B373" s="18">
+      <c r="B373" s="17">
         <v>44516</v>
       </c>
       <c r="C373" s="8" t="s">
@@ -20890,10 +20897,10 @@
       </c>
     </row>
     <row r="374" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A374" s="17">
+      <c r="A374" s="16">
         <v>100993</v>
       </c>
-      <c r="B374" s="18">
+      <c r="B374" s="17">
         <v>44516</v>
       </c>
       <c r="C374" s="8" t="s">
@@ -20922,10 +20929,10 @@
       </c>
     </row>
     <row r="375" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A375" s="17">
+      <c r="A375" s="16">
         <v>100994</v>
       </c>
-      <c r="B375" s="18">
+      <c r="B375" s="17">
         <v>44517</v>
       </c>
       <c r="C375" s="8" t="s">
@@ -20954,10 +20961,10 @@
       </c>
     </row>
     <row r="376" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A376" s="17">
+      <c r="A376" s="16">
         <v>100259</v>
       </c>
-      <c r="B376" s="18">
+      <c r="B376" s="17">
         <v>44518</v>
       </c>
       <c r="C376" s="8" t="s">
@@ -20986,10 +20993,10 @@
       </c>
     </row>
     <row r="377" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A377" s="17">
+      <c r="A377" s="16">
         <v>100273</v>
       </c>
-      <c r="B377" s="18">
+      <c r="B377" s="17">
         <v>44519</v>
       </c>
       <c r="C377" s="8" t="s">
@@ -21018,10 +21025,10 @@
       </c>
     </row>
     <row r="378" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A378" s="17">
+      <c r="A378" s="16">
         <v>100996</v>
       </c>
-      <c r="B378" s="18">
+      <c r="B378" s="17">
         <v>44519</v>
       </c>
       <c r="C378" s="8" t="s">
@@ -21050,10 +21057,10 @@
       </c>
     </row>
     <row r="379" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A379" s="17">
+      <c r="A379" s="16">
         <v>100998</v>
       </c>
-      <c r="B379" s="18">
+      <c r="B379" s="17">
         <v>44519</v>
       </c>
       <c r="C379" s="8" t="s">
@@ -21082,10 +21089,10 @@
       </c>
     </row>
     <row r="380" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A380" s="17">
+      <c r="A380" s="16">
         <v>100999</v>
       </c>
-      <c r="B380" s="18">
+      <c r="B380" s="17">
         <v>44519</v>
       </c>
       <c r="C380" s="8" t="s">
@@ -21114,10 +21121,10 @@
       </c>
     </row>
     <row r="381" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A381" s="17">
+      <c r="A381" s="16">
         <v>101000</v>
       </c>
-      <c r="B381" s="18">
+      <c r="B381" s="17">
         <v>44519</v>
       </c>
       <c r="C381" s="8" t="s">
@@ -21146,10 +21153,10 @@
       </c>
     </row>
     <row r="382" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A382" s="17">
+      <c r="A382" s="16">
         <v>100257</v>
       </c>
-      <c r="B382" s="18">
+      <c r="B382" s="17">
         <v>44520</v>
       </c>
       <c r="C382" s="8" t="s">
@@ -21178,10 +21185,10 @@
       </c>
     </row>
     <row r="383" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A383" s="17">
+      <c r="A383" s="16">
         <v>100258</v>
       </c>
-      <c r="B383" s="18">
+      <c r="B383" s="17">
         <v>44521</v>
       </c>
       <c r="C383" s="8" t="s">
@@ -21210,10 +21217,10 @@
       </c>
     </row>
     <row r="384" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A384" s="17">
+      <c r="A384" s="16">
         <v>101003</v>
       </c>
-      <c r="B384" s="18">
+      <c r="B384" s="17">
         <v>44521</v>
       </c>
       <c r="C384" s="8" t="s">
@@ -21242,10 +21249,10 @@
       </c>
     </row>
     <row r="385" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A385" s="17">
+      <c r="A385" s="16">
         <v>101005</v>
       </c>
-      <c r="B385" s="18">
+      <c r="B385" s="17">
         <v>44521</v>
       </c>
       <c r="C385" s="8" t="s">
@@ -21274,10 +21281,10 @@
       </c>
     </row>
     <row r="386" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A386" s="17">
+      <c r="A386" s="16">
         <v>100208</v>
       </c>
-      <c r="B386" s="18">
+      <c r="B386" s="17">
         <v>44522</v>
       </c>
       <c r="C386" s="8" t="s">
@@ -21306,10 +21313,10 @@
       </c>
     </row>
     <row r="387" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A387" s="17">
+      <c r="A387" s="16">
         <v>101008</v>
       </c>
-      <c r="B387" s="18">
+      <c r="B387" s="17">
         <v>44522</v>
       </c>
       <c r="C387" s="8" t="s">
@@ -21338,10 +21345,10 @@
       </c>
     </row>
     <row r="388" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A388" s="17">
+      <c r="A388" s="16">
         <v>101009</v>
       </c>
-      <c r="B388" s="18">
+      <c r="B388" s="17">
         <v>44522</v>
       </c>
       <c r="C388" s="8" t="s">
@@ -21370,10 +21377,10 @@
       </c>
     </row>
     <row r="389" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A389" s="17">
+      <c r="A389" s="16">
         <v>100307</v>
       </c>
-      <c r="B389" s="18">
+      <c r="B389" s="17">
         <v>44523</v>
       </c>
       <c r="C389" s="8" t="s">
@@ -21402,10 +21409,10 @@
       </c>
     </row>
     <row r="390" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A390" s="17">
+      <c r="A390" s="16">
         <v>101011</v>
       </c>
-      <c r="B390" s="18">
+      <c r="B390" s="17">
         <v>44523</v>
       </c>
       <c r="C390" s="8" t="s">
@@ -21434,10 +21441,10 @@
       </c>
     </row>
     <row r="391" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A391" s="17">
+      <c r="A391" s="16">
         <v>101012</v>
       </c>
-      <c r="B391" s="18">
+      <c r="B391" s="17">
         <v>44524</v>
       </c>
       <c r="C391" s="8" t="s">
@@ -21466,10 +21473,10 @@
       </c>
     </row>
     <row r="392" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A392" s="17">
+      <c r="A392" s="16">
         <v>100271</v>
       </c>
-      <c r="B392" s="18">
+      <c r="B392" s="17">
         <v>44525</v>
       </c>
       <c r="C392" s="8" t="s">
@@ -21498,10 +21505,10 @@
       </c>
     </row>
     <row r="393" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A393" s="17">
+      <c r="A393" s="16">
         <v>100301</v>
       </c>
-      <c r="B393" s="18">
+      <c r="B393" s="17">
         <v>44525</v>
       </c>
       <c r="C393" s="8" t="s">
@@ -21530,10 +21537,10 @@
       </c>
     </row>
     <row r="394" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A394" s="17">
+      <c r="A394" s="16">
         <v>101016</v>
       </c>
-      <c r="B394" s="18">
+      <c r="B394" s="17">
         <v>44525</v>
       </c>
       <c r="C394" s="8" t="s">
@@ -21562,10 +21569,10 @@
       </c>
     </row>
     <row r="395" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A395" s="17">
+      <c r="A395" s="16">
         <v>101019</v>
       </c>
-      <c r="B395" s="18">
+      <c r="B395" s="17">
         <v>44526</v>
       </c>
       <c r="C395" s="8" t="s">
@@ -21594,10 +21601,10 @@
       </c>
     </row>
     <row r="396" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A396" s="17">
+      <c r="A396" s="16">
         <v>100336</v>
       </c>
-      <c r="B396" s="18">
+      <c r="B396" s="17">
         <v>44527</v>
       </c>
       <c r="C396" s="8" t="s">
@@ -21626,10 +21633,10 @@
       </c>
     </row>
     <row r="397" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A397" s="17">
+      <c r="A397" s="16">
         <v>101023</v>
       </c>
-      <c r="B397" s="18">
+      <c r="B397" s="17">
         <v>44527</v>
       </c>
       <c r="C397" s="8" t="s">
@@ -21658,10 +21665,10 @@
       </c>
     </row>
     <row r="398" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A398" s="17">
+      <c r="A398" s="16">
         <v>101024</v>
       </c>
-      <c r="B398" s="18">
+      <c r="B398" s="17">
         <v>44527</v>
       </c>
       <c r="C398" s="8" t="s">
@@ -21690,10 +21697,10 @@
       </c>
     </row>
     <row r="399" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A399" s="17">
+      <c r="A399" s="16">
         <v>100206</v>
       </c>
-      <c r="B399" s="18">
+      <c r="B399" s="17">
         <v>44528</v>
       </c>
       <c r="C399" s="8" t="s">
@@ -21722,10 +21729,10 @@
       </c>
     </row>
     <row r="400" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A400" s="17">
+      <c r="A400" s="16">
         <v>100286</v>
       </c>
-      <c r="B400" s="18">
+      <c r="B400" s="17">
         <v>44528</v>
       </c>
       <c r="C400" s="8" t="s">
@@ -21754,10 +21761,10 @@
       </c>
     </row>
     <row r="401" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A401" s="17">
+      <c r="A401" s="16">
         <v>100324</v>
       </c>
-      <c r="B401" s="18">
+      <c r="B401" s="17">
         <v>44528</v>
       </c>
       <c r="C401" s="8" t="s">
@@ -21786,10 +21793,10 @@
       </c>
     </row>
     <row r="402" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A402" s="17">
+      <c r="A402" s="16">
         <v>100334</v>
       </c>
-      <c r="B402" s="18">
+      <c r="B402" s="17">
         <v>44528</v>
       </c>
       <c r="C402" s="8" t="s">
@@ -21818,10 +21825,10 @@
       </c>
     </row>
     <row r="403" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A403" s="17">
+      <c r="A403" s="16">
         <v>100335</v>
       </c>
-      <c r="B403" s="18">
+      <c r="B403" s="17">
         <v>44528</v>
       </c>
       <c r="C403" s="8" t="s">
@@ -21850,10 +21857,10 @@
       </c>
     </row>
     <row r="404" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A404" s="17">
+      <c r="A404" s="16">
         <v>101025</v>
       </c>
-      <c r="B404" s="18">
+      <c r="B404" s="17">
         <v>44528</v>
       </c>
       <c r="C404" s="8" t="s">
@@ -21882,10 +21889,10 @@
       </c>
     </row>
     <row r="405" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A405" s="17">
+      <c r="A405" s="16">
         <v>101029</v>
       </c>
-      <c r="B405" s="18">
+      <c r="B405" s="17">
         <v>44528</v>
       </c>
       <c r="C405" s="8" t="s">
@@ -21914,10 +21921,10 @@
       </c>
     </row>
     <row r="406" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A406" s="17">
+      <c r="A406" s="16">
         <v>101031</v>
       </c>
-      <c r="B406" s="18">
+      <c r="B406" s="17">
         <v>44529</v>
       </c>
       <c r="C406" s="8" t="s">
@@ -21946,10 +21953,10 @@
       </c>
     </row>
     <row r="407" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A407" s="17">
+      <c r="A407" s="16">
         <v>100205</v>
       </c>
-      <c r="B407" s="18">
+      <c r="B407" s="17">
         <v>44530</v>
       </c>
       <c r="C407" s="8" t="s">
@@ -21978,10 +21985,10 @@
       </c>
     </row>
     <row r="408" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A408" s="17">
+      <c r="A408" s="16">
         <v>100222</v>
       </c>
-      <c r="B408" s="18">
+      <c r="B408" s="17">
         <v>44530</v>
       </c>
       <c r="C408" s="8" t="s">
@@ -22010,10 +22017,10 @@
       </c>
     </row>
     <row r="409" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A409" s="17">
+      <c r="A409" s="16">
         <v>101034</v>
       </c>
-      <c r="B409" s="18">
+      <c r="B409" s="17">
         <v>44530</v>
       </c>
       <c r="C409" s="8" t="s">
@@ -22042,10 +22049,10 @@
       </c>
     </row>
     <row r="410" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A410" s="17">
+      <c r="A410" s="16">
         <v>100221</v>
       </c>
-      <c r="B410" s="18">
+      <c r="B410" s="17">
         <v>44531</v>
       </c>
       <c r="C410" s="8" t="s">
@@ -22074,10 +22081,10 @@
       </c>
     </row>
     <row r="411" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A411" s="17">
+      <c r="A411" s="16">
         <v>100246</v>
       </c>
-      <c r="B411" s="18">
+      <c r="B411" s="17">
         <v>44531</v>
       </c>
       <c r="C411" s="8" t="s">
@@ -22106,10 +22113,10 @@
       </c>
     </row>
     <row r="412" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A412" s="17">
+      <c r="A412" s="16">
         <v>100298</v>
       </c>
-      <c r="B412" s="18">
+      <c r="B412" s="17">
         <v>44531</v>
       </c>
       <c r="C412" s="8" t="s">
@@ -22138,10 +22145,10 @@
       </c>
     </row>
     <row r="413" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A413" s="17">
+      <c r="A413" s="16">
         <v>101035</v>
       </c>
-      <c r="B413" s="18">
+      <c r="B413" s="17">
         <v>44531</v>
       </c>
       <c r="C413" s="8" t="s">
@@ -22170,10 +22177,10 @@
       </c>
     </row>
     <row r="414" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A414" s="17">
+      <c r="A414" s="16">
         <v>100333</v>
       </c>
-      <c r="B414" s="18">
+      <c r="B414" s="17">
         <v>44532</v>
       </c>
       <c r="C414" s="8" t="s">
@@ -22202,10 +22209,10 @@
       </c>
     </row>
     <row r="415" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A415" s="17">
+      <c r="A415" s="16">
         <v>101036</v>
       </c>
-      <c r="B415" s="18">
+      <c r="B415" s="17">
         <v>44532</v>
       </c>
       <c r="C415" s="8" t="s">
@@ -22234,10 +22241,10 @@
       </c>
     </row>
     <row r="416" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A416" s="17">
+      <c r="A416" s="16">
         <v>101037</v>
       </c>
-      <c r="B416" s="18">
+      <c r="B416" s="17">
         <v>44532</v>
       </c>
       <c r="C416" s="8" t="s">
@@ -22266,10 +22273,10 @@
       </c>
     </row>
     <row r="417" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A417" s="17">
+      <c r="A417" s="16">
         <v>101039</v>
       </c>
-      <c r="B417" s="18">
+      <c r="B417" s="17">
         <v>44533</v>
       </c>
       <c r="C417" s="8" t="s">
@@ -22298,10 +22305,10 @@
       </c>
     </row>
     <row r="418" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A418" s="17">
+      <c r="A418" s="16">
         <v>101042</v>
       </c>
-      <c r="B418" s="18">
+      <c r="B418" s="17">
         <v>44533</v>
       </c>
       <c r="C418" s="8" t="s">
@@ -22330,10 +22337,10 @@
       </c>
     </row>
     <row r="419" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A419" s="17">
+      <c r="A419" s="16">
         <v>101043</v>
       </c>
-      <c r="B419" s="18">
+      <c r="B419" s="17">
         <v>44534</v>
       </c>
       <c r="C419" s="8" t="s">
@@ -22362,10 +22369,10 @@
       </c>
     </row>
     <row r="420" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A420" s="17">
+      <c r="A420" s="16">
         <v>101044</v>
       </c>
-      <c r="B420" s="18">
+      <c r="B420" s="17">
         <v>44534</v>
       </c>
       <c r="C420" s="8" t="s">
@@ -22394,10 +22401,10 @@
       </c>
     </row>
     <row r="421" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A421" s="17">
+      <c r="A421" s="16">
         <v>100219</v>
       </c>
-      <c r="B421" s="18">
+      <c r="B421" s="17">
         <v>44535</v>
       </c>
       <c r="C421" s="8" t="s">
@@ -22426,10 +22433,10 @@
       </c>
     </row>
     <row r="422" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A422" s="17">
+      <c r="A422" s="16">
         <v>100220</v>
       </c>
-      <c r="B422" s="18">
+      <c r="B422" s="17">
         <v>44535</v>
       </c>
       <c r="C422" s="8" t="s">
@@ -22458,10 +22465,10 @@
       </c>
     </row>
     <row r="423" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A423" s="17">
+      <c r="A423" s="16">
         <v>100235</v>
       </c>
-      <c r="B423" s="18">
+      <c r="B423" s="17">
         <v>44535</v>
       </c>
       <c r="C423" s="8" t="s">
@@ -22490,10 +22497,10 @@
       </c>
     </row>
     <row r="424" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A424" s="17">
+      <c r="A424" s="16">
         <v>100300</v>
       </c>
-      <c r="B424" s="18">
+      <c r="B424" s="17">
         <v>44535</v>
       </c>
       <c r="C424" s="8" t="s">
@@ -22522,10 +22529,10 @@
       </c>
     </row>
     <row r="425" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A425" s="17">
+      <c r="A425" s="16">
         <v>101046</v>
       </c>
-      <c r="B425" s="18">
+      <c r="B425" s="17">
         <v>44535</v>
       </c>
       <c r="C425" s="8" t="s">
@@ -22554,10 +22561,10 @@
       </c>
     </row>
     <row r="426" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A426" s="17">
+      <c r="A426" s="16">
         <v>100366</v>
       </c>
-      <c r="B426" s="18">
+      <c r="B426" s="17">
         <v>44537</v>
       </c>
       <c r="C426" s="8" t="s">
@@ -22586,10 +22593,10 @@
       </c>
     </row>
     <row r="427" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A427" s="17">
+      <c r="A427" s="16">
         <v>101052</v>
       </c>
-      <c r="B427" s="18">
+      <c r="B427" s="17">
         <v>44537</v>
       </c>
       <c r="C427" s="8" t="s">
@@ -22618,10 +22625,10 @@
       </c>
     </row>
     <row r="428" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A428" s="17">
+      <c r="A428" s="16">
         <v>101053</v>
       </c>
-      <c r="B428" s="18">
+      <c r="B428" s="17">
         <v>44537</v>
       </c>
       <c r="C428" s="8" t="s">
@@ -22650,10 +22657,10 @@
       </c>
     </row>
     <row r="429" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A429" s="17">
+      <c r="A429" s="16">
         <v>101054</v>
       </c>
-      <c r="B429" s="18">
+      <c r="B429" s="17">
         <v>44537</v>
       </c>
       <c r="C429" s="8" t="s">
@@ -22682,10 +22689,10 @@
       </c>
     </row>
     <row r="430" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A430" s="17">
+      <c r="A430" s="16">
         <v>100234</v>
       </c>
-      <c r="B430" s="18">
+      <c r="B430" s="17">
         <v>44538</v>
       </c>
       <c r="C430" s="8" t="s">
@@ -22714,10 +22721,10 @@
       </c>
     </row>
     <row r="431" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A431" s="17">
+      <c r="A431" s="16">
         <v>100269</v>
       </c>
-      <c r="B431" s="18">
+      <c r="B431" s="17">
         <v>44539</v>
       </c>
       <c r="C431" s="8" t="s">
@@ -22746,10 +22753,10 @@
       </c>
     </row>
     <row r="432" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A432" s="17">
+      <c r="A432" s="16">
         <v>100317</v>
       </c>
-      <c r="B432" s="18">
+      <c r="B432" s="17">
         <v>44539</v>
       </c>
       <c r="C432" s="8" t="s">
@@ -22778,10 +22785,10 @@
       </c>
     </row>
     <row r="433" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A433" s="17">
+      <c r="A433" s="16">
         <v>100318</v>
       </c>
-      <c r="B433" s="18">
+      <c r="B433" s="17">
         <v>44539</v>
       </c>
       <c r="C433" s="8" t="s">
@@ -22810,10 +22817,10 @@
       </c>
     </row>
     <row r="434" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A434" s="17">
+      <c r="A434" s="16">
         <v>100319</v>
       </c>
-      <c r="B434" s="18">
+      <c r="B434" s="17">
         <v>44539</v>
       </c>
       <c r="C434" s="8" t="s">
@@ -22842,10 +22849,10 @@
       </c>
     </row>
     <row r="435" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A435" s="17">
+      <c r="A435" s="16">
         <v>101058</v>
       </c>
-      <c r="B435" s="18">
+      <c r="B435" s="17">
         <v>44539</v>
       </c>
       <c r="C435" s="8" t="s">
@@ -22874,10 +22881,10 @@
       </c>
     </row>
     <row r="436" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A436" s="17">
+      <c r="A436" s="16">
         <v>101061</v>
       </c>
-      <c r="B436" s="18">
+      <c r="B436" s="17">
         <v>44539</v>
       </c>
       <c r="C436" s="8" t="s">
@@ -22906,10 +22913,10 @@
       </c>
     </row>
     <row r="437" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A437" s="17">
+      <c r="A437" s="16">
         <v>100365</v>
       </c>
-      <c r="B437" s="18">
+      <c r="B437" s="17">
         <v>44540</v>
       </c>
       <c r="C437" s="8" t="s">
@@ -22938,10 +22945,10 @@
       </c>
     </row>
     <row r="438" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A438" s="17">
+      <c r="A438" s="16">
         <v>100374</v>
       </c>
-      <c r="B438" s="18">
+      <c r="B438" s="17">
         <v>44541</v>
       </c>
       <c r="C438" s="8" t="s">
@@ -22970,10 +22977,10 @@
       </c>
     </row>
     <row r="439" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A439" s="17">
+      <c r="A439" s="16">
         <v>101066</v>
       </c>
-      <c r="B439" s="18">
+      <c r="B439" s="17">
         <v>44541</v>
       </c>
       <c r="C439" s="8" t="s">
@@ -23002,10 +23009,10 @@
       </c>
     </row>
     <row r="440" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A440" s="17">
+      <c r="A440" s="16">
         <v>101067</v>
       </c>
-      <c r="B440" s="18">
+      <c r="B440" s="17">
         <v>44541</v>
       </c>
       <c r="C440" s="8" t="s">
@@ -23034,10 +23041,10 @@
       </c>
     </row>
     <row r="441" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A441" s="17">
+      <c r="A441" s="16">
         <v>101068</v>
       </c>
-      <c r="B441" s="18">
+      <c r="B441" s="17">
         <v>44541</v>
       </c>
       <c r="C441" s="8" t="s">
@@ -23066,10 +23073,10 @@
       </c>
     </row>
     <row r="442" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A442" s="17">
+      <c r="A442" s="16">
         <v>100244</v>
       </c>
-      <c r="B442" s="18">
+      <c r="B442" s="17">
         <v>44542</v>
       </c>
       <c r="C442" s="8" t="s">
@@ -23098,10 +23105,10 @@
       </c>
     </row>
     <row r="443" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A443" s="17">
+      <c r="A443" s="16">
         <v>101069</v>
       </c>
-      <c r="B443" s="18">
+      <c r="B443" s="17">
         <v>44542</v>
       </c>
       <c r="C443" s="8" t="s">
@@ -23130,10 +23137,10 @@
       </c>
     </row>
     <row r="444" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A444" s="17">
+      <c r="A444" s="16">
         <v>101070</v>
       </c>
-      <c r="B444" s="18">
+      <c r="B444" s="17">
         <v>44542</v>
       </c>
       <c r="C444" s="8" t="s">
@@ -23162,10 +23169,10 @@
       </c>
     </row>
     <row r="445" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A445" s="17">
+      <c r="A445" s="16">
         <v>101071</v>
       </c>
-      <c r="B445" s="18">
+      <c r="B445" s="17">
         <v>44542</v>
       </c>
       <c r="C445" s="8" t="s">
@@ -23194,10 +23201,10 @@
       </c>
     </row>
     <row r="446" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A446" s="17">
+      <c r="A446" s="16">
         <v>101073</v>
       </c>
-      <c r="B446" s="18">
+      <c r="B446" s="17">
         <v>44543</v>
       </c>
       <c r="C446" s="8" t="s">
@@ -23226,10 +23233,10 @@
       </c>
     </row>
     <row r="447" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A447" s="17">
+      <c r="A447" s="16">
         <v>101074</v>
       </c>
-      <c r="B447" s="18">
+      <c r="B447" s="17">
         <v>44543</v>
       </c>
       <c r="C447" s="8" t="s">
@@ -23258,10 +23265,10 @@
       </c>
     </row>
     <row r="448" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A448" s="17">
+      <c r="A448" s="16">
         <v>100364</v>
       </c>
-      <c r="B448" s="18">
+      <c r="B448" s="17">
         <v>44544</v>
       </c>
       <c r="C448" s="8" t="s">
@@ -23290,10 +23297,10 @@
       </c>
     </row>
     <row r="449" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A449" s="17">
+      <c r="A449" s="16">
         <v>101075</v>
       </c>
-      <c r="B449" s="18">
+      <c r="B449" s="17">
         <v>44544</v>
       </c>
       <c r="C449" s="8" t="s">
@@ -23322,10 +23329,10 @@
       </c>
     </row>
     <row r="450" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A450" s="17">
+      <c r="A450" s="16">
         <v>101076</v>
       </c>
-      <c r="B450" s="18">
+      <c r="B450" s="17">
         <v>44544</v>
       </c>
       <c r="C450" s="8" t="s">
@@ -23354,10 +23361,10 @@
       </c>
     </row>
     <row r="451" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A451" s="17">
+      <c r="A451" s="16">
         <v>100218</v>
       </c>
-      <c r="B451" s="18">
+      <c r="B451" s="17">
         <v>44547</v>
       </c>
       <c r="C451" s="8" t="s">
@@ -23386,10 +23393,10 @@
       </c>
     </row>
     <row r="452" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A452" s="17">
+      <c r="A452" s="16">
         <v>101083</v>
       </c>
-      <c r="B452" s="18">
+      <c r="B452" s="17">
         <v>44548</v>
       </c>
       <c r="C452" s="8" t="s">
@@ -23418,10 +23425,10 @@
       </c>
     </row>
     <row r="453" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A453" s="17">
+      <c r="A453" s="16">
         <v>101088</v>
       </c>
-      <c r="B453" s="18">
+      <c r="B453" s="17">
         <v>44549</v>
       </c>
       <c r="C453" s="8" t="s">
@@ -23450,10 +23457,10 @@
       </c>
     </row>
     <row r="454" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A454" s="17">
+      <c r="A454" s="16">
         <v>101089</v>
       </c>
-      <c r="B454" s="18">
+      <c r="B454" s="17">
         <v>44549</v>
       </c>
       <c r="C454" s="8" t="s">
@@ -23482,10 +23489,10 @@
       </c>
     </row>
     <row r="455" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A455" s="17">
+      <c r="A455" s="16">
         <v>101090</v>
       </c>
-      <c r="B455" s="18">
+      <c r="B455" s="17">
         <v>44549</v>
       </c>
       <c r="C455" s="8" t="s">
@@ -23514,10 +23521,10 @@
       </c>
     </row>
     <row r="456" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A456" s="17">
+      <c r="A456" s="16">
         <v>101091</v>
       </c>
-      <c r="B456" s="18">
+      <c r="B456" s="17">
         <v>44549</v>
       </c>
       <c r="C456" s="8" t="s">
@@ -23546,10 +23553,10 @@
       </c>
     </row>
     <row r="457" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A457" s="17">
+      <c r="A457" s="16">
         <v>101092</v>
       </c>
-      <c r="B457" s="18">
+      <c r="B457" s="17">
         <v>44549</v>
       </c>
       <c r="C457" s="8" t="s">
@@ -23578,10 +23585,10 @@
       </c>
     </row>
     <row r="458" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A458" s="17">
+      <c r="A458" s="16">
         <v>101093</v>
       </c>
-      <c r="B458" s="18">
+      <c r="B458" s="17">
         <v>44549</v>
       </c>
       <c r="C458" s="8" t="s">
@@ -23610,10 +23617,10 @@
       </c>
     </row>
     <row r="459" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A459" s="17">
+      <c r="A459" s="16">
         <v>100347</v>
       </c>
-      <c r="B459" s="18">
+      <c r="B459" s="17">
         <v>44550</v>
       </c>
       <c r="C459" s="8" t="s">
@@ -23642,10 +23649,10 @@
       </c>
     </row>
     <row r="460" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A460" s="17">
+      <c r="A460" s="16">
         <v>101094</v>
       </c>
-      <c r="B460" s="18">
+      <c r="B460" s="17">
         <v>44550</v>
       </c>
       <c r="C460" s="8" t="s">
@@ -23674,10 +23681,10 @@
       </c>
     </row>
     <row r="461" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A461" s="17">
+      <c r="A461" s="16">
         <v>100204</v>
       </c>
-      <c r="B461" s="18">
+      <c r="B461" s="17">
         <v>44551</v>
       </c>
       <c r="C461" s="8" t="s">
@@ -23706,10 +23713,10 @@
       </c>
     </row>
     <row r="462" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A462" s="17">
+      <c r="A462" s="16">
         <v>100344</v>
       </c>
-      <c r="B462" s="18">
+      <c r="B462" s="17">
         <v>44551</v>
       </c>
       <c r="C462" s="8" t="s">
@@ -23738,10 +23745,10 @@
       </c>
     </row>
     <row r="463" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A463" s="17">
+      <c r="A463" s="16">
         <v>100346</v>
       </c>
-      <c r="B463" s="18">
+      <c r="B463" s="17">
         <v>44551</v>
       </c>
       <c r="C463" s="8" t="s">
@@ -23770,10 +23777,10 @@
       </c>
     </row>
     <row r="464" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A464" s="17">
+      <c r="A464" s="16">
         <v>100391</v>
       </c>
-      <c r="B464" s="18">
+      <c r="B464" s="17">
         <v>44551</v>
       </c>
       <c r="C464" s="8" t="s">
@@ -23802,10 +23809,10 @@
       </c>
     </row>
     <row r="465" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A465" s="17">
+      <c r="A465" s="16">
         <v>101096</v>
       </c>
-      <c r="B465" s="18">
+      <c r="B465" s="17">
         <v>44551</v>
       </c>
       <c r="C465" s="8" t="s">
@@ -23834,10 +23841,10 @@
       </c>
     </row>
     <row r="466" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A466" s="17">
+      <c r="A466" s="16">
         <v>100203</v>
       </c>
-      <c r="B466" s="18">
+      <c r="B466" s="17">
         <v>44552</v>
       </c>
       <c r="C466" s="8" t="s">
@@ -23866,10 +23873,10 @@
       </c>
     </row>
     <row r="467" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A467" s="17">
+      <c r="A467" s="16">
         <v>100231</v>
       </c>
-      <c r="B467" s="18">
+      <c r="B467" s="17">
         <v>44552</v>
       </c>
       <c r="C467" s="8" t="s">
@@ -23898,10 +23905,10 @@
       </c>
     </row>
     <row r="468" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A468" s="17">
+      <c r="A468" s="16">
         <v>101098</v>
       </c>
-      <c r="B468" s="18">
+      <c r="B468" s="17">
         <v>44552</v>
       </c>
       <c r="C468" s="8" t="s">
@@ -23930,10 +23937,10 @@
       </c>
     </row>
     <row r="469" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A469" s="17">
+      <c r="A469" s="16">
         <v>101100</v>
       </c>
-      <c r="B469" s="18">
+      <c r="B469" s="17">
         <v>44552</v>
       </c>
       <c r="C469" s="8" t="s">
@@ -23962,10 +23969,10 @@
       </c>
     </row>
     <row r="470" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A470" s="17">
+      <c r="A470" s="16">
         <v>100202</v>
       </c>
-      <c r="B470" s="18">
+      <c r="B470" s="17">
         <v>44553</v>
       </c>
       <c r="C470" s="8" t="s">
@@ -23994,10 +24001,10 @@
       </c>
     </row>
     <row r="471" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A471" s="17">
+      <c r="A471" s="16">
         <v>100217</v>
       </c>
-      <c r="B471" s="18">
+      <c r="B471" s="17">
         <v>44553</v>
       </c>
       <c r="C471" s="8" t="s">
@@ -24026,10 +24033,10 @@
       </c>
     </row>
     <row r="472" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A472" s="17">
+      <c r="A472" s="16">
         <v>101102</v>
       </c>
-      <c r="B472" s="18">
+      <c r="B472" s="17">
         <v>44553</v>
       </c>
       <c r="C472" s="8" t="s">
@@ -24058,10 +24065,10 @@
       </c>
     </row>
     <row r="473" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A473" s="17">
+      <c r="A473" s="16">
         <v>100305</v>
       </c>
-      <c r="B473" s="18">
+      <c r="B473" s="17">
         <v>44554</v>
       </c>
       <c r="C473" s="8" t="s">
@@ -24090,10 +24097,10 @@
       </c>
     </row>
     <row r="474" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A474" s="17">
+      <c r="A474" s="16">
         <v>101104</v>
       </c>
-      <c r="B474" s="18">
+      <c r="B474" s="17">
         <v>44554</v>
       </c>
       <c r="C474" s="8" t="s">
@@ -24122,10 +24129,10 @@
       </c>
     </row>
     <row r="475" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A475" s="17">
+      <c r="A475" s="16">
         <v>101105</v>
       </c>
-      <c r="B475" s="18">
+      <c r="B475" s="17">
         <v>44554</v>
       </c>
       <c r="C475" s="8" t="s">
@@ -24154,10 +24161,10 @@
       </c>
     </row>
     <row r="476" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A476" s="17">
+      <c r="A476" s="16">
         <v>100201</v>
       </c>
-      <c r="B476" s="18">
+      <c r="B476" s="17">
         <v>44555</v>
       </c>
       <c r="C476" s="8" t="s">
@@ -24186,10 +24193,10 @@
       </c>
     </row>
     <row r="477" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A477" s="17">
+      <c r="A477" s="16">
         <v>100230</v>
       </c>
-      <c r="B477" s="18">
+      <c r="B477" s="17">
         <v>44555</v>
       </c>
       <c r="C477" s="8" t="s">
@@ -24218,10 +24225,10 @@
       </c>
     </row>
     <row r="478" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A478" s="17">
+      <c r="A478" s="16">
         <v>100295</v>
       </c>
-      <c r="B478" s="18">
+      <c r="B478" s="17">
         <v>44555</v>
       </c>
       <c r="C478" s="8" t="s">
@@ -24250,10 +24257,10 @@
       </c>
     </row>
     <row r="479" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A479" s="17">
+      <c r="A479" s="16">
         <v>100360</v>
       </c>
-      <c r="B479" s="18">
+      <c r="B479" s="17">
         <v>44555</v>
       </c>
       <c r="C479" s="8" t="s">
@@ -24282,10 +24289,10 @@
       </c>
     </row>
     <row r="480" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A480" s="17">
+      <c r="A480" s="16">
         <v>100361</v>
       </c>
-      <c r="B480" s="18">
+      <c r="B480" s="17">
         <v>44555</v>
       </c>
       <c r="C480" s="8" t="s">
@@ -24314,10 +24321,10 @@
       </c>
     </row>
     <row r="481" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A481" s="17">
+      <c r="A481" s="16">
         <v>101107</v>
       </c>
-      <c r="B481" s="18">
+      <c r="B481" s="17">
         <v>44555</v>
       </c>
       <c r="C481" s="8" t="s">
@@ -24346,10 +24353,10 @@
       </c>
     </row>
     <row r="482" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A482" s="17">
+      <c r="A482" s="16">
         <v>101109</v>
       </c>
-      <c r="B482" s="18">
+      <c r="B482" s="17">
         <v>44555</v>
       </c>
       <c r="C482" s="8" t="s">
@@ -24378,10 +24385,10 @@
       </c>
     </row>
     <row r="483" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A483" s="17">
+      <c r="A483" s="16">
         <v>100229</v>
       </c>
-      <c r="B483" s="18">
+      <c r="B483" s="17">
         <v>44556</v>
       </c>
       <c r="C483" s="8" t="s">
@@ -24410,10 +24417,10 @@
       </c>
     </row>
     <row r="484" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A484" s="17">
+      <c r="A484" s="16">
         <v>100282</v>
       </c>
-      <c r="B484" s="18">
+      <c r="B484" s="17">
         <v>44556</v>
       </c>
       <c r="C484" s="8" t="s">
@@ -24442,10 +24449,10 @@
       </c>
     </row>
     <row r="485" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A485" s="17">
+      <c r="A485" s="16">
         <v>101111</v>
       </c>
-      <c r="B485" s="18">
+      <c r="B485" s="17">
         <v>44556</v>
       </c>
       <c r="C485" s="8" t="s">
@@ -24474,10 +24481,10 @@
       </c>
     </row>
     <row r="486" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A486" s="17">
+      <c r="A486" s="16">
         <v>100400</v>
       </c>
-      <c r="B486" s="18">
+      <c r="B486" s="17">
         <v>44557</v>
       </c>
       <c r="C486" s="8" t="s">
@@ -24506,10 +24513,10 @@
       </c>
     </row>
     <row r="487" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A487" s="17">
+      <c r="A487" s="16">
         <v>101113</v>
       </c>
-      <c r="B487" s="18">
+      <c r="B487" s="17">
         <v>44557</v>
       </c>
       <c r="C487" s="8" t="s">
@@ -24538,10 +24545,10 @@
       </c>
     </row>
     <row r="488" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A488" s="17">
+      <c r="A488" s="16">
         <v>101114</v>
       </c>
-      <c r="B488" s="18">
+      <c r="B488" s="17">
         <v>44557</v>
       </c>
       <c r="C488" s="8" t="s">
@@ -24570,10 +24577,10 @@
       </c>
     </row>
     <row r="489" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A489" s="17">
+      <c r="A489" s="16">
         <v>100200</v>
       </c>
-      <c r="B489" s="18">
+      <c r="B489" s="17">
         <v>44558</v>
       </c>
       <c r="C489" s="8" t="s">
@@ -24602,10 +24609,10 @@
       </c>
     </row>
     <row r="490" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A490" s="17">
+      <c r="A490" s="16">
         <v>100330</v>
       </c>
-      <c r="B490" s="18">
+      <c r="B490" s="17">
         <v>44558</v>
       </c>
       <c r="C490" s="8" t="s">
@@ -24634,10 +24641,10 @@
       </c>
     </row>
     <row r="491" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A491" s="17">
+      <c r="A491" s="16">
         <v>101115</v>
       </c>
-      <c r="B491" s="18">
+      <c r="B491" s="17">
         <v>44558</v>
       </c>
       <c r="C491" s="8" t="s">
@@ -24666,10 +24673,10 @@
       </c>
     </row>
     <row r="492" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A492" s="17">
+      <c r="A492" s="16">
         <v>101116</v>
       </c>
-      <c r="B492" s="18">
+      <c r="B492" s="17">
         <v>44559</v>
       </c>
       <c r="C492" s="8" t="s">
@@ -24698,10 +24705,10 @@
       </c>
     </row>
     <row r="493" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A493" s="17">
+      <c r="A493" s="16">
         <v>100216</v>
       </c>
-      <c r="B493" s="18">
+      <c r="B493" s="17">
         <v>44560</v>
       </c>
       <c r="C493" s="8" t="s">
@@ -24730,10 +24737,10 @@
       </c>
     </row>
     <row r="494" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A494" s="17">
+      <c r="A494" s="16">
         <v>100389</v>
       </c>
-      <c r="B494" s="18">
+      <c r="B494" s="17">
         <v>44560</v>
       </c>
       <c r="C494" s="8" t="s">
@@ -24762,10 +24769,10 @@
       </c>
     </row>
     <row r="495" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A495" s="17">
+      <c r="A495" s="16">
         <v>101117</v>
       </c>
-      <c r="B495" s="18">
+      <c r="B495" s="17">
         <v>44560</v>
       </c>
       <c r="C495" s="8" t="s">
@@ -24794,10 +24801,10 @@
       </c>
     </row>
     <row r="496" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A496" s="17">
+      <c r="A496" s="16">
         <v>101120</v>
       </c>
-      <c r="B496" s="18">
+      <c r="B496" s="17">
         <v>44560</v>
       </c>
       <c r="C496" s="8" t="s">
@@ -24826,10 +24833,10 @@
       </c>
     </row>
     <row r="497" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A497" s="17">
+      <c r="A497" s="16">
         <v>101121</v>
       </c>
-      <c r="B497" s="18">
+      <c r="B497" s="17">
         <v>44561</v>
       </c>
       <c r="C497" s="8" t="s">
@@ -24858,10 +24865,10 @@
       </c>
     </row>
     <row r="498" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A498" s="17">
+      <c r="A498" s="16">
         <v>101122</v>
       </c>
-      <c r="B498" s="18">
+      <c r="B498" s="17">
         <v>44561</v>
       </c>
       <c r="C498" s="8" t="s">
@@ -24890,10 +24897,10 @@
       </c>
     </row>
     <row r="499" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A499" s="17">
+      <c r="A499" s="16">
         <v>101123</v>
       </c>
-      <c r="B499" s="18">
+      <c r="B499" s="17">
         <v>44561</v>
       </c>
       <c r="C499" s="8" t="s">
@@ -24922,10 +24929,10 @@
       </c>
     </row>
     <row r="500" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A500" s="17">
+      <c r="A500" s="16">
         <v>101125</v>
       </c>
-      <c r="B500" s="18">
+      <c r="B500" s="17">
         <v>44561</v>
       </c>
       <c r="C500" s="8" t="s">
@@ -24954,10 +24961,10 @@
       </c>
     </row>
     <row r="501" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A501" s="17">
+      <c r="A501" s="16">
         <v>101126</v>
       </c>
-      <c r="B501" s="18">
+      <c r="B501" s="17">
         <v>44561</v>
       </c>
       <c r="C501" s="8" t="s">
